--- a/analise_financeira.xlsx
+++ b/analise_financeira.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F325"/>
+  <dimension ref="A1:F329"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3787,22 +3787,22 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>1707817</t>
+          <t>1707510</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>138.680,75</t>
+          <t>11.962,34</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>382.282,74</t>
+          <t>37.895,39</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>-R$ 243.601,99</t>
+          <t>-R$ 25.933,05</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -3812,51 +3812,51 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>-63.7%</t>
+          <t>-68.4%</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>1708066</t>
+          <t>1707817</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>3.419,06</t>
+          <t>138.680,75</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>382.282,74</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>R$ 3.419,06</t>
+          <t>-R$ 243.601,99</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-63.7%</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>1708877</t>
+          <t>1708066</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>3,54</t>
+          <t>3.419,06</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -3866,7 +3866,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>R$ 3,54</t>
+          <t>R$ 3.419,06</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -3883,12 +3883,12 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>1708877I</t>
+          <t>1708877</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>2.132,72</t>
+          <t>3,54</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -3898,7 +3898,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>R$ 2.132,72</t>
+          <t>R$ 3,54</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -3915,12 +3915,12 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>1708906</t>
+          <t>1708877I</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>7.652,25</t>
+          <t>2.132,72</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -3930,7 +3930,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>R$ 7.652,25</t>
+          <t>R$ 2.132,72</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -3947,22 +3947,22 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>1708908</t>
+          <t>1708906</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>34.163,18</t>
+          <t>7.652,25</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>29.400,43</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>R$ 4.762,75</t>
+          <t>R$ 7.652,25</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -3972,115 +3972,115 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>+16.2%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>1709419</t>
+          <t>1708908</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>34.163,18</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>29.400,43</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 4.762,75</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+16.2%</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>1709486</t>
+          <t>1709419</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>6.291,40</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>47.063,85</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>-R$ 40.772,45</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>-86.6%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>1709995</t>
+          <t>1709486</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>2.410,16</t>
+          <t>6.291,40</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>47.063,85</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>R$ 2.410,16</t>
+          <t>-R$ 40.772,45</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-86.6%</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>1710116</t>
+          <t>1709995</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>2.410,16</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 2.410,16</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4107,54 +4107,54 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>1710220</t>
+          <t>1710116</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>2.270,95</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>2.270,94</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>R$ 0,01</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>+0.0%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>1710287C</t>
+          <t>1710220</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>56,80</t>
+          <t>2.270,95</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>2.270,94</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>R$ 56,80</t>
+          <t>R$ 0,01</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -4164,19 +4164,19 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.0%</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>1710287I</t>
+          <t>1710287C</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>8.740,43</t>
+          <t>56,80</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -4186,7 +4186,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>R$ 8.740,43</t>
+          <t>R$ 56,80</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -4203,22 +4203,22 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>1710322</t>
+          <t>1710287I</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>190.028,30</t>
+          <t>8.740,43</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>176.859,43</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>R$ 13.168,87</t>
+          <t>R$ 8.740,43</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -4228,29 +4228,29 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>+7.4%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>1710329</t>
+          <t>1710322</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>24.211,86</t>
+          <t>190.028,30</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>176.859,43</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>R$ 24.211,86</t>
+          <t>R$ 13.168,87</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -4260,19 +4260,19 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+7.4%</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>1710332</t>
+          <t>1710329</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>223,64</t>
+          <t>24.211,86</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -4282,7 +4282,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>R$ 223,64</t>
+          <t>R$ 24.211,86</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -4299,12 +4299,12 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>1710735</t>
+          <t>1710332</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>9.751,61</t>
+          <t>223,64</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -4314,7 +4314,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>R$ 9.751,61</t>
+          <t>R$ 223,64</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -4331,12 +4331,12 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>1710736</t>
+          <t>1710735</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>9.751,61</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -4346,12 +4346,12 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 9.751,61</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4363,12 +4363,12 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>1710937</t>
+          <t>1710736</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>4.234,81</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -4378,12 +4378,12 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>R$ 4.234,81</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4395,12 +4395,12 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>1710975</t>
+          <t>1710937</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>913,41</t>
+          <t>4.234,81</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -4410,7 +4410,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>R$ 913,41</t>
+          <t>R$ 4.234,81</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -4427,12 +4427,12 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>1711110</t>
+          <t>1710975</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>913,41</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -4442,12 +4442,12 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 913,41</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4459,76 +4459,76 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>1711378</t>
+          <t>1711110</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>9.934,10</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>10.727,58</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>-R$ 793,48</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>-7.4%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>1711384</t>
+          <t>1711378</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>2.250,33</t>
+          <t>9.934,10</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>10.727,58</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>R$ 2.250,33</t>
+          <t>-R$ 793,48</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-7.4%</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>1711454</t>
+          <t>1711384</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>10.429,60</t>
+          <t>2.250,33</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -4538,7 +4538,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>R$ 10.429,60</t>
+          <t>R$ 2.250,33</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -4555,86 +4555,86 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>1711489</t>
+          <t>1711454</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>4.381,49</t>
+          <t>10.429,60</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>73.801,59</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>-R$ 69.420,10</t>
+          <t>R$ 10.429,60</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>-94.1%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>1711507</t>
+          <t>1711489</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>15.939,34</t>
+          <t>4.381,49</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>13.503,20</t>
+          <t>73.801,59</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>R$ 2.436,14</t>
+          <t>-R$ 69.420,10</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>+18.0%</t>
+          <t>-94.1%</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>1711525</t>
+          <t>1711507</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>2.125,35</t>
+          <t>15.939,34</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>13.503,20</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>R$ 2.125,35</t>
+          <t>R$ 2.436,14</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -4644,61 +4644,61 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+18.0%</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>1711629</t>
+          <t>1711525</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>4.201,07</t>
+          <t>2.125,35</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>13.482,28</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>-R$ 9.281,21</t>
+          <t>R$ 2.125,35</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>-68.8%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>1711775</t>
+          <t>1711629</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>1.932,93</t>
+          <t>4.201,07</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>2.356,20</t>
+          <t>13.482,28</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>-R$ 423,27</t>
+          <t>-R$ 9.281,21</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -4708,29 +4708,29 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>-18.0%</t>
+          <t>-68.8%</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>1711788</t>
+          <t>1711775</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>8.104,03</t>
+          <t>1.932,93</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>13.482,28</t>
+          <t>2.356,20</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>-R$ 5.378,25</t>
+          <t>-R$ 423,27</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -4740,51 +4740,51 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>-39.9%</t>
+          <t>-18.0%</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>1712530</t>
+          <t>1711788</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>6.922,75</t>
+          <t>8.104,03</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>13.482,28</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>R$ 6.922,75</t>
+          <t>-R$ 5.378,25</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-39.9%</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>1712531</t>
+          <t>1712530</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>5.019,99</t>
+          <t>6.922,75</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -4794,7 +4794,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>R$ 5.019,99</t>
+          <t>R$ 6.922,75</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -4811,12 +4811,12 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>1712533</t>
+          <t>1712531</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>2.680,86</t>
+          <t>5.019,99</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>R$ 2.680,86</t>
+          <t>R$ 5.019,99</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -4843,12 +4843,12 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>1712538</t>
+          <t>1712533</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>3.955,41</t>
+          <t>2.680,86</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -4858,7 +4858,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>R$ 3.955,41</t>
+          <t>R$ 2.680,86</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -4875,12 +4875,12 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>1712547</t>
+          <t>1712538</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>7.069,45</t>
+          <t>3.955,41</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>R$ 7.069,45</t>
+          <t>R$ 3.955,41</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -4907,12 +4907,12 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>1712550</t>
+          <t>1712547</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>5.007,08</t>
+          <t>7.069,45</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -4922,7 +4922,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>R$ 5.007,08</t>
+          <t>R$ 7.069,45</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -4939,12 +4939,12 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>1712624</t>
+          <t>1712550</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>3.073,90</t>
+          <t>5.007,08</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -4954,7 +4954,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>R$ 3.073,90</t>
+          <t>R$ 5.007,08</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -4971,12 +4971,12 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>1712766</t>
+          <t>1712624</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>705,45</t>
+          <t>3.073,90</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -4986,7 +4986,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>R$ 705,45</t>
+          <t>R$ 3.073,90</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -5003,12 +5003,12 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>1712957</t>
+          <t>1712766</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>2.222,83</t>
+          <t>705,45</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>R$ 2.222,83</t>
+          <t>R$ 705,45</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -5035,12 +5035,12 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>1712963I</t>
+          <t>1712957</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>12.285,61</t>
+          <t>2.222,83</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -5050,7 +5050,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>R$ 12.285,61</t>
+          <t>R$ 2.222,83</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -5067,12 +5067,12 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>1713044C</t>
+          <t>1712963I</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>21,11</t>
+          <t>12.285,61</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -5082,7 +5082,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>R$ 21,11</t>
+          <t>R$ 12.285,61</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -5099,12 +5099,12 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>1713044I</t>
+          <t>1713044C</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>1.528,53</t>
+          <t>21,11</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -5114,7 +5114,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>R$ 1.528,53</t>
+          <t>R$ 21,11</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -5131,76 +5131,76 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>1713045</t>
+          <t>1713044I</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>29.639,83</t>
+          <t>1.528,53</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>205.265,15</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>-R$ 175.625,32</t>
+          <t>R$ 1.528,53</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>-85.6%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>1713221</t>
+          <t>1713045</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>18.794,09</t>
+          <t>29.639,83</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>205.265,15</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>R$ 18.794,09</t>
+          <t>-R$ 175.625,32</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-85.6%</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>1713223</t>
+          <t>1713221</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>13.438,83</t>
+          <t>18.794,09</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -5210,7 +5210,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>R$ 13.438,83</t>
+          <t>R$ 18.794,09</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -5227,12 +5227,12 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>1713226</t>
+          <t>1713223</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>3.287,04</t>
+          <t>13.438,83</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -5242,7 +5242,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>R$ 3.287,04</t>
+          <t>R$ 13.438,83</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -5259,12 +5259,12 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>1713240</t>
+          <t>1713226</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>5.108,11</t>
+          <t>3.287,04</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -5274,7 +5274,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>R$ 5.108,11</t>
+          <t>R$ 3.287,04</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -5291,76 +5291,76 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>1713260</t>
+          <t>1713240</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>10.803,62</t>
+          <t>5.108,11</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>73.801,59</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>-R$ 62.997,97</t>
+          <t>R$ 5.108,11</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>-85.4%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>1713262</t>
+          <t>1713260</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>2.675,61</t>
+          <t>10.803,62</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>73.801,59</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>R$ 2.675,61</t>
+          <t>-R$ 62.997,97</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-85.4%</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>1713351</t>
+          <t>1713262</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>622,97</t>
+          <t>2.675,61</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -5370,7 +5370,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>R$ 622,97</t>
+          <t>R$ 2.675,61</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -5387,12 +5387,12 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>1713435I</t>
+          <t>1713351</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>622,97</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -5402,12 +5402,12 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 622,97</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
@@ -5419,12 +5419,12 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>1713626</t>
+          <t>1713435I</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>161,42</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -5434,12 +5434,12 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>R$ 161,42</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -5451,12 +5451,12 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>1713626I</t>
+          <t>1713626</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>5.318,80</t>
+          <t>161,42</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -5466,7 +5466,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>R$ 5.318,80</t>
+          <t>R$ 161,42</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -5483,12 +5483,12 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>1713656</t>
+          <t>1713626I</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>4.315,58</t>
+          <t>5.318,80</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -5498,7 +5498,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>R$ 4.315,58</t>
+          <t>R$ 5.318,80</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -5515,12 +5515,12 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>1713656I</t>
+          <t>1713656</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>161,74</t>
+          <t>4.315,58</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -5530,7 +5530,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>R$ 161,74</t>
+          <t>R$ 4.315,58</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -5547,12 +5547,12 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>1713660</t>
+          <t>1713656I</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>161,11</t>
+          <t>161,74</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -5562,7 +5562,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>R$ 161,11</t>
+          <t>R$ 161,74</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -5579,12 +5579,12 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>1713679</t>
+          <t>1713660</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>3.574,44</t>
+          <t>161,11</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -5594,7 +5594,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>R$ 3.574,44</t>
+          <t>R$ 161,11</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -5611,76 +5611,76 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>1713681</t>
+          <t>1713679</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>1.473,94</t>
+          <t>3.574,44</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>13.482,28</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>-R$ 12.008,34</t>
+          <t>R$ 3.574,44</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>-89.1%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>1713719</t>
+          <t>1713681</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>3.385,92</t>
+          <t>1.473,94</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>13.482,28</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>R$ 3.385,92</t>
+          <t>-R$ 12.008,34</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-89.1%</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>1713903C</t>
+          <t>1713719</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>36,14</t>
+          <t>3.385,92</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -5690,7 +5690,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>R$ 36,14</t>
+          <t>R$ 3.385,92</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -5707,12 +5707,12 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>1713903I</t>
+          <t>1713903C</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>972,91</t>
+          <t>36,14</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -5722,7 +5722,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>R$ 972,91</t>
+          <t>R$ 36,14</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -5739,12 +5739,12 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>1713916</t>
+          <t>1713903I</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>4.815,09</t>
+          <t>972,91</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -5754,7 +5754,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>R$ 4.815,09</t>
+          <t>R$ 972,91</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -5771,12 +5771,12 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>1713933</t>
+          <t>1713916</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>5.530,92</t>
+          <t>4.815,09</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -5786,7 +5786,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>R$ 5.530,92</t>
+          <t>R$ 4.815,09</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -5803,86 +5803,86 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>1714342</t>
+          <t>1713933</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>2.011,96</t>
+          <t>5.530,92</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>22.187,97</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>-R$ 20.176,01</t>
+          <t>R$ 5.530,92</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>-90.9%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>1714348</t>
+          <t>1714342</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>8.422,88</t>
+          <t>2.011,96</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>6.874,07</t>
+          <t>22.187,97</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>R$ 1.548,81</t>
+          <t>-R$ 20.176,01</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>+22.5%</t>
+          <t>-90.9%</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>1714364</t>
+          <t>1714348</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>54,64</t>
+          <t>8.422,88</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>6.874,07</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>R$ 54,64</t>
+          <t>R$ 1.548,81</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
@@ -5892,83 +5892,83 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+22.5%</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>1714699</t>
+          <t>1714364</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>25.018,29</t>
+          <t>54,64</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>55.022,87</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>-R$ 30.004,58</t>
+          <t>R$ 54,64</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>-54.5%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>1714729</t>
+          <t>1714699</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>6.722,61</t>
+          <t>25.018,29</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>55.022,87</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>R$ 6.722,61</t>
+          <t>-R$ 30.004,58</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-54.5%</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>1714857</t>
+          <t>1714729</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>185,07</t>
+          <t>6.722,61</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -5978,7 +5978,7 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>R$ 185,07</t>
+          <t>R$ 6.722,61</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
@@ -5995,12 +5995,12 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>1714909</t>
+          <t>1714857</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>1.062,57</t>
+          <t>185,07</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -6010,7 +6010,7 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>R$ 1.062,57</t>
+          <t>R$ 185,07</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
@@ -6027,12 +6027,12 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>1715127</t>
+          <t>1714909</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>4.547,25</t>
+          <t>1.062,57</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -6042,7 +6042,7 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>R$ 4.547,25</t>
+          <t>R$ 1.062,57</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
@@ -6059,12 +6059,12 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>1715131</t>
+          <t>1715127</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>2.220,22</t>
+          <t>4.547,25</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -6074,7 +6074,7 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>R$ 2.220,22</t>
+          <t>R$ 4.547,25</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
@@ -6091,12 +6091,12 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>1715154</t>
+          <t>1715131</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>2.658,74</t>
+          <t>2.220,22</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -6106,7 +6106,7 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>R$ 2.658,74</t>
+          <t>R$ 2.220,22</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
@@ -6123,12 +6123,12 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>1715201</t>
+          <t>1715154</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>6.990,57</t>
+          <t>2.658,74</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -6138,7 +6138,7 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>R$ 6.990,57</t>
+          <t>R$ 2.658,74</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
@@ -6155,12 +6155,12 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>1715257I</t>
+          <t>1715201</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>6.765,65</t>
+          <t>6.990,57</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -6170,7 +6170,7 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>R$ 6.765,65</t>
+          <t>R$ 6.990,57</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
@@ -6187,12 +6187,12 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>1715278</t>
+          <t>1715257I</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>2.961,13</t>
+          <t>6.765,65</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -6202,7 +6202,7 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>R$ 2.961,13</t>
+          <t>R$ 6.765,65</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
@@ -6219,12 +6219,12 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>1715327</t>
+          <t>1715278</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>5.483,37</t>
+          <t>2.961,13</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -6234,7 +6234,7 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>R$ 5.483,37</t>
+          <t>R$ 2.961,13</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
@@ -6251,12 +6251,12 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>1715668</t>
+          <t>1715327</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>2.319,53</t>
+          <t>5.483,37</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -6266,7 +6266,7 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>R$ 2.319,53</t>
+          <t>R$ 5.483,37</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
@@ -6283,76 +6283,76 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>1715688</t>
+          <t>1715668</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>11.094,98</t>
+          <t>2.319,53</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>73.801,59</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>-R$ 62.706,61</t>
+          <t>R$ 2.319,53</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>-85.0%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>1715710</t>
+          <t>1715688</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>326,74</t>
+          <t>11.094,98</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>73.801,59</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>R$ 326,74</t>
+          <t>-R$ 62.706,61</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-85.0%</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>1715816C</t>
+          <t>1715710</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>30,22</t>
+          <t>326,74</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -6362,7 +6362,7 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>R$ 30,22</t>
+          <t>R$ 326,74</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
@@ -6379,12 +6379,12 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>1715816I</t>
+          <t>1715816C</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>3.168,40</t>
+          <t>30,22</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -6394,7 +6394,7 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>R$ 3.168,40</t>
+          <t>R$ 30,22</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
@@ -6411,12 +6411,12 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>1715878</t>
+          <t>1715816I</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>1.786,71</t>
+          <t>3.168,40</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -6426,7 +6426,7 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>R$ 1.786,71</t>
+          <t>R$ 3.168,40</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
@@ -6443,76 +6443,76 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>1715899</t>
+          <t>1715878</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>3.389,65</t>
+          <t>1.786,71</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>30.150,78</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>-R$ 26.761,13</t>
+          <t>R$ 1.786,71</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>-88.8%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>1715920</t>
+          <t>1715899</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>1.031,94</t>
+          <t>3.389,65</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>30.150,78</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>R$ 1.031,94</t>
+          <t>-R$ 26.761,13</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-88.8%</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>1715955I</t>
+          <t>1715920</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>4.431,48</t>
+          <t>1.031,94</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -6522,7 +6522,7 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>R$ 4.431,48</t>
+          <t>R$ 1.031,94</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
@@ -6539,44 +6539,44 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>1716557</t>
+          <t>1715955I</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>81.673,94</t>
+          <t>4.431,48</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>219.995,37</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>-R$ 138.321,43</t>
+          <t>R$ 4.431,48</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>-62.9%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>1716612</t>
+          <t>1716557</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>113.404,80</t>
+          <t>81.673,94</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -6586,7 +6586,7 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>-R$ 106.590,57</t>
+          <t>-R$ 138.321,43</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
@@ -6596,29 +6596,29 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>-48.5%</t>
+          <t>-62.9%</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>1717166</t>
+          <t>1716612</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>22.116,83</t>
+          <t>113.404,80</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>73.801,59</t>
+          <t>219.995,37</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>-R$ 51.684,76</t>
+          <t>-R$ 106.590,57</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
@@ -6628,29 +6628,29 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>-70.0%</t>
+          <t>-48.5%</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>1717168</t>
+          <t>1717166</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>2.615,74</t>
+          <t>22.116,83</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>30.150,78</t>
+          <t>73.801,59</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>-R$ 27.535,04</t>
+          <t>-R$ 51.684,76</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
@@ -6660,29 +6660,29 @@
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>-91.3%</t>
+          <t>-70.0%</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>1717315</t>
+          <t>1717168</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>13.183,29</t>
+          <t>2.615,74</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>13.214,86</t>
+          <t>30.150,78</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>-R$ 31,57</t>
+          <t>-R$ 27.535,04</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
@@ -6692,93 +6692,93 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>-0.2%</t>
+          <t>-91.3%</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>1717332</t>
+          <t>1717315</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>2.496,51</t>
+          <t>13.183,29</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>13.214,86</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>R$ 2.496,51</t>
+          <t>-R$ 31,57</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.2%</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>1718019</t>
+          <t>1717332</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>4.408,31</t>
+          <t>2.496,51</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>28.774,45</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>-R$ 24.366,14</t>
+          <t>R$ 2.496,51</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>-84.7%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>1718435</t>
+          <t>1718019</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>17.153,90</t>
+          <t>4.408,31</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>40.717,37</t>
+          <t>28.774,45</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>-R$ 23.563,47</t>
+          <t>-R$ 24.366,14</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
@@ -6788,29 +6788,29 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>-57.9%</t>
+          <t>-84.7%</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>1718441</t>
+          <t>1718435</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>85.675,14</t>
+          <t>17.153,90</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>102.545,06</t>
+          <t>40.717,37</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>-R$ 16.869,92</t>
+          <t>-R$ 23.563,47</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
@@ -6820,51 +6820,51 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>-16.5%</t>
+          <t>-57.9%</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>1718442</t>
+          <t>1718441</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>3.206,15</t>
+          <t>85.675,14</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>102.545,06</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>R$ 3.206,15</t>
+          <t>-R$ 16.869,92</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-16.5%</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>1718555</t>
+          <t>1718442</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>80,49</t>
+          <t>3.206,15</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -6874,7 +6874,7 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>R$ 80,49</t>
+          <t>R$ 3.206,15</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
@@ -6891,12 +6891,12 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>1718555I</t>
+          <t>1718555</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>2.781,60</t>
+          <t>80,49</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -6906,7 +6906,7 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>R$ 2.781,60</t>
+          <t>R$ 80,49</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
@@ -6923,12 +6923,12 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>1718561</t>
+          <t>1718555I</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>15.227,27</t>
+          <t>2.781,60</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -6938,7 +6938,7 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>R$ 15.227,27</t>
+          <t>R$ 2.781,60</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
@@ -6955,12 +6955,12 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>1718783</t>
+          <t>1718561</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>16.983,02</t>
+          <t>15.227,27</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -6970,7 +6970,7 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>R$ 16.983,02</t>
+          <t>R$ 15.227,27</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
@@ -6987,118 +6987,118 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>1718783C</t>
+          <t>1718783</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>7,32</t>
+          <t>16.983,02</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>40.717,37</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>-R$ 40.710,05</t>
+          <t>R$ 16.983,02</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>-100.0%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>1718803</t>
+          <t>1718783C</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>3.825,18</t>
+          <t>7,32</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>40.717,37</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>R$ 3.825,18</t>
+          <t>-R$ 40.710,05</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-100.0%</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>1718950</t>
+          <t>1718803</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>65.537,44</t>
+          <t>3.825,18</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>104.023,78</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>-R$ 38.486,34</t>
+          <t>R$ 3.825,18</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>-37.0%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>1718951</t>
+          <t>1718950</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>257,86</t>
+          <t>65.537,44</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>59.203,65</t>
+          <t>104.023,78</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>-R$ 58.945,79</t>
+          <t>-R$ 38.486,34</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
@@ -7108,29 +7108,29 @@
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>-99.6%</t>
+          <t>-37.0%</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>1718954</t>
+          <t>1718951</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>16.304,49</t>
+          <t>257,86</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>45.853,04</t>
+          <t>59.203,65</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>-R$ 29.548,55</t>
+          <t>-R$ 58.945,79</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
@@ -7140,29 +7140,29 @@
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>-64.4%</t>
+          <t>-99.6%</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>1718956</t>
+          <t>1718954</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>34.745,40</t>
+          <t>16.304,49</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>104.023,78</t>
+          <t>45.853,04</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>-R$ 69.278,38</t>
+          <t>-R$ 29.548,55</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
@@ -7172,29 +7172,29 @@
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>-66.6%</t>
+          <t>-64.4%</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>1718958</t>
+          <t>1718956</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>28.287,18</t>
+          <t>34.745,40</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>45.853,04</t>
+          <t>104.023,78</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>-R$ 17.565,86</t>
+          <t>-R$ 69.278,38</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
@@ -7204,93 +7204,93 @@
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>-38.3%</t>
+          <t>-66.6%</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>1719070</t>
+          <t>1718958</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>3.077,85</t>
+          <t>28.287,18</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>45.853,04</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>R$ 3.077,85</t>
+          <t>-R$ 17.565,86</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-38.3%</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>1719077</t>
+          <t>1719070</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>12.241,72</t>
+          <t>3.077,85</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>55.391,23</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>-R$ 43.149,51</t>
+          <t>R$ 3.077,85</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>-77.9%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>1719097</t>
+          <t>1719077</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>7.450,28</t>
+          <t>12.241,72</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>17.534,63</t>
+          <t>55.391,23</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>-R$ 10.084,35</t>
+          <t>-R$ 43.149,51</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
@@ -7300,93 +7300,93 @@
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>-57.5%</t>
+          <t>-77.9%</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>1719135</t>
+          <t>1719097</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>960,92</t>
+          <t>7.450,28</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>17.534,63</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>R$ 960,92</t>
+          <t>-R$ 10.084,35</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-57.5%</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>1719154</t>
+          <t>1719135</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>2.574,70</t>
+          <t>960,92</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>73.801,59</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>-R$ 71.226,89</t>
+          <t>R$ 960,92</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>-96.5%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>1719155</t>
+          <t>1719154</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>2.368,97</t>
+          <t>2.574,70</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>30.150,78</t>
+          <t>73.801,59</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>-R$ 27.781,81</t>
+          <t>-R$ 71.226,89</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
@@ -7396,29 +7396,29 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>-92.1%</t>
+          <t>-96.5%</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>1719159</t>
+          <t>1719155</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>2.240,81</t>
+          <t>2.368,97</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>22.187,97</t>
+          <t>30.150,78</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>-R$ 19.947,16</t>
+          <t>-R$ 27.781,81</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
@@ -7428,29 +7428,29 @@
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>-89.9%</t>
+          <t>-92.1%</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>1719213</t>
+          <t>1719159</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>7.323,19</t>
+          <t>2.240,81</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>30.150,78</t>
+          <t>22.187,97</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>-R$ 22.827,59</t>
+          <t>-R$ 19.947,16</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
@@ -7460,29 +7460,29 @@
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>-75.7%</t>
+          <t>-89.9%</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>1719214</t>
+          <t>1719213</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>6.124,60</t>
+          <t>7.323,19</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>28.774,45</t>
+          <t>30.150,78</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>-R$ 22.649,85</t>
+          <t>-R$ 22.827,59</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
@@ -7492,29 +7492,29 @@
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>-78.7%</t>
+          <t>-75.7%</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>1719775</t>
+          <t>1719214</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>6.946,00</t>
+          <t>6.124,60</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>10.782,30</t>
+          <t>28.774,45</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>-R$ 3.836,30</t>
+          <t>-R$ 22.649,85</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
@@ -7524,157 +7524,157 @@
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>-35.6%</t>
+          <t>-78.7%</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>1719881</t>
+          <t>1719488</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>3.239,73</t>
+          <t>10.023,26</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>205.265,15</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>R$ 3.239,73</t>
+          <t>-R$ 195.241,89</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-95.1%</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>1719881H</t>
+          <t>1719775</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>38.258,42</t>
+          <t>6.946,00</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>10.782,30</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>R$ 38.258,42</t>
+          <t>-R$ 3.836,30</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-35.6%</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>1720116</t>
+          <t>1719881</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>1.844,52</t>
+          <t>3.239,73</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>28.774,45</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>-R$ 26.929,93</t>
+          <t>R$ 3.239,73</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>-93.6%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>1720721</t>
+          <t>1719881H</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>2.015,45</t>
+          <t>38.258,42</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>17.534,63</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>-R$ 15.519,18</t>
+          <t>R$ 38.258,42</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>-88.5%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>1720909</t>
+          <t>1720116</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>2.851,89</t>
+          <t>1.844,52</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>7.731,21</t>
+          <t>28.774,45</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>-R$ 4.879,32</t>
+          <t>-R$ 26.929,93</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
@@ -7684,29 +7684,29 @@
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>-63.1%</t>
+          <t>-93.6%</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>1720914</t>
+          <t>1720721</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>16.536,50</t>
+          <t>2.015,45</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>55.022,87</t>
+          <t>17.534,63</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>-R$ 38.486,37</t>
+          <t>-R$ 15.519,18</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
@@ -7716,61 +7716,61 @@
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>-69.9%</t>
+          <t>-88.5%</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>1720920</t>
+          <t>1720909</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>644,89</t>
+          <t>2.851,89</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>7.731,21</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>R$ 644,89</t>
+          <t>-R$ 4.879,32</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-63.1%</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>1721175</t>
+          <t>1720914</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>1.191,73</t>
+          <t>16.536,50</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>22.187,97</t>
+          <t>55.022,87</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>-R$ 20.996,24</t>
+          <t>-R$ 38.486,37</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
@@ -7780,61 +7780,61 @@
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>-94.6%</t>
+          <t>-69.9%</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>1721180</t>
+          <t>1720920</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>7.835,70</t>
+          <t>644,89</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>13.305,24</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>-R$ 5.469,54</t>
+          <t>R$ 644,89</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>-41.1%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>1721595</t>
+          <t>1721175</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>2.704,41</t>
+          <t>1.191,73</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>16.337,54</t>
+          <t>22.187,97</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>-R$ 13.633,13</t>
+          <t>-R$ 20.996,24</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
@@ -7844,61 +7844,61 @@
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>-83.4%</t>
+          <t>-94.6%</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>1721631</t>
+          <t>1721180</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>12.649,43</t>
+          <t>7.835,70</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>13.305,24</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>R$ 12.649,43</t>
+          <t>-R$ 5.469,54</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-41.1%</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>1721631C</t>
+          <t>1721595</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>100,65</t>
+          <t>2.704,41</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>17.534,63</t>
+          <t>16.337,54</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>-R$ 17.433,98</t>
+          <t>-R$ 13.633,13</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
@@ -7908,61 +7908,61 @@
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>-99.4%</t>
+          <t>-83.4%</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>1721869</t>
+          <t>1721631</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>940,27</t>
+          <t>12.649,43</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>25.002,10</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>-R$ 24.061,83</t>
+          <t>R$ 12.649,43</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>-96.2%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>1721884</t>
+          <t>1721631C</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>41.481,66</t>
+          <t>100,65</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>205.265,15</t>
+          <t>17.534,63</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>-R$ 163.783,49</t>
+          <t>-R$ 17.433,98</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
@@ -7972,29 +7972,29 @@
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>-79.8%</t>
+          <t>-99.4%</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>1721886</t>
+          <t>1721869</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>15.863,55</t>
+          <t>940,27</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>55.022,87</t>
+          <t>25.002,10</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>-R$ 39.159,32</t>
+          <t>-R$ 24.061,83</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
@@ -8004,29 +8004,29 @@
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>-71.2%</t>
+          <t>-96.2%</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>1721887</t>
+          <t>1721884</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>15.229,27</t>
+          <t>41.481,66</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>60.918,10</t>
+          <t>205.265,15</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>-R$ 45.688,83</t>
+          <t>-R$ 163.783,49</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
@@ -8036,29 +8036,29 @@
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>-75.0%</t>
+          <t>-79.8%</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>1722165</t>
+          <t>1721886</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>23.880,34</t>
+          <t>15.863,55</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>294.803,26</t>
+          <t>55.022,87</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>-R$ 270.922,92</t>
+          <t>-R$ 39.159,32</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
@@ -8068,61 +8068,61 @@
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>-91.9%</t>
+          <t>-71.2%</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>1722169</t>
+          <t>1721887</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>39.464,29</t>
+          <t>15.229,27</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>60.918,10</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>R$ 39.464,29</t>
+          <t>-R$ 45.688,83</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-75.0%</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>1722320</t>
+          <t>1722165</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>12.790,83</t>
+          <t>23.880,34</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>30.150,78</t>
+          <t>294.803,26</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>-R$ 17.359,95</t>
+          <t>-R$ 270.922,92</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
@@ -8132,61 +8132,61 @@
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>-57.6%</t>
+          <t>-91.9%</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>1722321</t>
+          <t>1722169</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>8.119,58</t>
+          <t>39.464,29</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>60.918,10</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>-R$ 52.798,52</t>
+          <t>R$ 39.464,29</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>-86.7%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>1722779</t>
+          <t>1722320</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>15.490,41</t>
+          <t>12.790,83</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>205.265,15</t>
+          <t>30.150,78</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>-R$ 189.774,74</t>
+          <t>-R$ 17.359,95</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
@@ -8196,29 +8196,29 @@
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>-92.5%</t>
+          <t>-57.6%</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>1722803</t>
+          <t>1722321</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>1.585,72</t>
+          <t>8.119,58</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>52.950,36</t>
+          <t>60.918,10</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>-R$ 51.364,64</t>
+          <t>-R$ 52.798,52</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
@@ -8228,29 +8228,29 @@
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>-97.0%</t>
+          <t>-86.7%</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>1722904</t>
+          <t>1722779</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>2.417,20</t>
+          <t>15.490,41</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>25.002,10</t>
+          <t>205.265,15</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>-R$ 22.584,90</t>
+          <t>-R$ 189.774,74</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
@@ -8260,29 +8260,29 @@
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>-90.3%</t>
+          <t>-92.5%</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>1722905</t>
+          <t>1722803</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>2.816,32</t>
+          <t>1.585,72</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>46.847,53</t>
+          <t>52.950,36</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>-R$ 44.031,21</t>
+          <t>-R$ 51.364,64</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
@@ -8292,61 +8292,61 @@
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>-94.0%</t>
+          <t>-97.0%</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>1722924</t>
+          <t>1722904</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>19.829,31</t>
+          <t>2.417,20</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>19.642,99</t>
+          <t>25.002,10</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>R$ 186,32</t>
+          <t>-R$ 22.584,90</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>+0.9%</t>
+          <t>-90.3%</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>1723691</t>
+          <t>1722905</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>19.599,32</t>
+          <t>2.816,32</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>151.495,34</t>
+          <t>46.847,53</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>-R$ 131.896,02</t>
+          <t>-R$ 44.031,21</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
@@ -8356,61 +8356,61 @@
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>-87.1%</t>
+          <t>-94.0%</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>1723694</t>
+          <t>1722924</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>3.867,23</t>
+          <t>19.829,31</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>7.731,21</t>
+          <t>19.642,99</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>-R$ 3.863,98</t>
+          <t>R$ 186,32</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>-50.0%</t>
+          <t>+0.9%</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>1723722</t>
+          <t>1723691</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>3.175,84</t>
+          <t>19.599,32</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>10.782,30</t>
+          <t>151.495,34</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>-R$ 7.606,46</t>
+          <t>-R$ 131.896,02</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
@@ -8420,29 +8420,29 @@
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>-70.5%</t>
+          <t>-87.1%</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>1723724</t>
+          <t>1723694</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>3.376,37</t>
+          <t>3.867,23</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>104.023,78</t>
+          <t>7.731,21</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>-R$ 100.647,41</t>
+          <t>-R$ 3.863,98</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
@@ -8452,29 +8452,29 @@
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>-96.8%</t>
+          <t>-50.0%</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>1723726</t>
+          <t>1723722</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>7.911,81</t>
+          <t>3.175,84</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>46.847,53</t>
+          <t>10.782,30</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>-R$ 38.935,72</t>
+          <t>-R$ 7.606,46</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
@@ -8484,29 +8484,29 @@
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>-83.1%</t>
+          <t>-70.5%</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>1723727</t>
+          <t>1723724</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>2.821,44</t>
+          <t>3.376,37</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>45.853,04</t>
+          <t>104.023,78</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>-R$ 43.031,60</t>
+          <t>-R$ 100.647,41</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
@@ -8516,29 +8516,29 @@
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>-93.8%</t>
+          <t>-96.8%</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>1724051I</t>
+          <t>1723726</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>2.432,48</t>
+          <t>7.911,81</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>151.495,34</t>
+          <t>46.847,53</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>-R$ 149.062,86</t>
+          <t>-R$ 38.935,72</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
@@ -8548,29 +8548,29 @@
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>-98.4%</t>
+          <t>-83.1%</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>1724053</t>
+          <t>1723727</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>3.088,86</t>
+          <t>2.821,44</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>151.495,34</t>
+          <t>45.853,04</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>-R$ 148.406,48</t>
+          <t>-R$ 43.031,60</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
@@ -8580,29 +8580,29 @@
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>-98.0%</t>
+          <t>-93.8%</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>1724172</t>
+          <t>1724051I</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>23.068,97</t>
+          <t>2.432,48</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>60.918,10</t>
+          <t>151.495,34</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>-R$ 37.849,13</t>
+          <t>-R$ 149.062,86</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
@@ -8612,51 +8612,51 @@
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>-62.1%</t>
+          <t>-98.4%</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>1724341</t>
+          <t>1724053</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>40.758,00</t>
+          <t>3.088,86</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>151.495,34</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>R$ 40.758,00</t>
+          <t>-R$ 148.406,48</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-98.0%</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>1724356</t>
+          <t>1724172</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>7.614,80</t>
+          <t>23.068,97</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
@@ -8666,7 +8666,7 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>-R$ 53.303,30</t>
+          <t>-R$ 37.849,13</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
@@ -8676,61 +8676,61 @@
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>-87.5%</t>
+          <t>-62.1%</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>1724491</t>
+          <t>1724341</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>14.410,93</t>
+          <t>40.758,00</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>24.535,37</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>-R$ 10.124,44</t>
+          <t>R$ 40.758,00</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>-41.3%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>1724537</t>
+          <t>1724356</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>8.464,00</t>
+          <t>7.614,80</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>19.215,26</t>
+          <t>60.918,10</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>-R$ 10.751,26</t>
+          <t>-R$ 53.303,30</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
@@ -8740,29 +8740,29 @@
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>-56.0%</t>
+          <t>-87.5%</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>1724550</t>
+          <t>1724491</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>17.067,84</t>
+          <t>14.410,93</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>55.391,23</t>
+          <t>24.535,37</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>-R$ 38.323,39</t>
+          <t>-R$ 10.124,44</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
@@ -8772,29 +8772,29 @@
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>-69.2%</t>
+          <t>-41.3%</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>1724551</t>
+          <t>1724537</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>8.569,24</t>
+          <t>8.464,00</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>59.203,65</t>
+          <t>19.215,26</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>-R$ 50.634,41</t>
+          <t>-R$ 10.751,26</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
@@ -8804,29 +8804,29 @@
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>-85.5%</t>
+          <t>-56.0%</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>1724558</t>
+          <t>1724550</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>10.501,47</t>
+          <t>17.067,84</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>151.495,34</t>
+          <t>55.391,23</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>-R$ 140.993,87</t>
+          <t>-R$ 38.323,39</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
@@ -8836,29 +8836,29 @@
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>-93.1%</t>
+          <t>-69.2%</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>1724663</t>
+          <t>1724551</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>3.091,28</t>
+          <t>8.569,24</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>22.187,97</t>
+          <t>59.203,65</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>-R$ 19.096,69</t>
+          <t>-R$ 50.634,41</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
@@ -8868,29 +8868,29 @@
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>-86.1%</t>
+          <t>-85.5%</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>1725260</t>
+          <t>1724558</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>4.726,63</t>
+          <t>10.501,47</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>30.884,03</t>
+          <t>151.495,34</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>-R$ 26.157,40</t>
+          <t>-R$ 140.993,87</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
@@ -8900,29 +8900,29 @@
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>-84.7%</t>
+          <t>-93.1%</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>1725686</t>
+          <t>1724663</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>11.173,06</t>
+          <t>3.091,28</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>24.535,37</t>
+          <t>22.187,97</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>-R$ 13.362,31</t>
+          <t>-R$ 19.096,69</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
@@ -8932,29 +8932,29 @@
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>-54.5%</t>
+          <t>-86.1%</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>1725738C</t>
+          <t>1724680</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>146,69</t>
+          <t>7.968,73</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>25.002,10</t>
+          <t>60.918,10</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>-R$ 24.855,41</t>
+          <t>-R$ 52.949,37</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
@@ -8964,29 +8964,29 @@
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>-99.4%</t>
+          <t>-86.9%</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>1725738I</t>
+          <t>1725260</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>16.959,62</t>
+          <t>4.726,63</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>25.002,10</t>
+          <t>30.884,03</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>-R$ 8.042,48</t>
+          <t>-R$ 26.157,40</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
@@ -8996,61 +8996,61 @@
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>-32.2%</t>
+          <t>-84.7%</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>1725869</t>
+          <t>1725686</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>2.488,83</t>
+          <t>11.173,06</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>24.535,37</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>R$ 2.488,83</t>
+          <t>-R$ 13.362,31</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-54.5%</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>1726007</t>
+          <t>1725738C</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>92.044,51</t>
+          <t>146,69</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>140.684,13</t>
+          <t>25.002,10</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>-R$ 48.639,62</t>
+          <t>-R$ 24.855,41</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
@@ -9060,29 +9060,29 @@
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>-34.6%</t>
+          <t>-99.4%</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>1726008</t>
+          <t>1725738I</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>168.057,63</t>
+          <t>16.959,62</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>203.193,73</t>
+          <t>25.002,10</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>-R$ 35.136,10</t>
+          <t>-R$ 8.042,48</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
@@ -9092,61 +9092,61 @@
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>-17.3%</t>
+          <t>-32.2%</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>1726018</t>
+          <t>1725869</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>117.487,61</t>
+          <t>2.488,83</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>189.306,13</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>-R$ 71.818,52</t>
+          <t>R$ 2.488,83</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>-37.9%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>1726042</t>
+          <t>1726007</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>52.831,30</t>
+          <t>92.044,51</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>192.548,30</t>
+          <t>140.684,13</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>-R$ 139.717,00</t>
+          <t>-R$ 48.639,62</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
@@ -9156,29 +9156,29 @@
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>-72.6%</t>
+          <t>-34.6%</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>1726044</t>
+          <t>1726008</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>163.324,35</t>
+          <t>168.057,63</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>167.292,84</t>
+          <t>203.193,73</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>-R$ 3.968,49</t>
+          <t>-R$ 35.136,10</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
@@ -9188,29 +9188,29 @@
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>-2.4%</t>
+          <t>-17.3%</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>1726045</t>
+          <t>1726018</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>114.693,62</t>
+          <t>117.487,61</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>126.996,75</t>
+          <t>189.306,13</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>-R$ 12.303,13</t>
+          <t>-R$ 71.818,52</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
@@ -9220,29 +9220,29 @@
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>-9.7%</t>
+          <t>-37.9%</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>1726057</t>
+          <t>1726042</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>177.769,55</t>
+          <t>52.831,30</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>196.508,79</t>
+          <t>192.548,30</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>-R$ 18.739,24</t>
+          <t>-R$ 139.717,00</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
@@ -9252,29 +9252,29 @@
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>-9.5%</t>
+          <t>-72.6%</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>1726058</t>
+          <t>1726044</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>103.529,88</t>
+          <t>163.324,35</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>133.354,34</t>
+          <t>167.292,84</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>-R$ 29.824,46</t>
+          <t>-R$ 3.968,49</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
@@ -9284,29 +9284,29 @@
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>-22.4%</t>
+          <t>-2.4%</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>1726318</t>
+          <t>1726045</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>17.722,33</t>
+          <t>114.693,62</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>55.391,23</t>
+          <t>126.996,75</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>-R$ 37.668,90</t>
+          <t>-R$ 12.303,13</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
@@ -9316,29 +9316,29 @@
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>-68.0%</t>
+          <t>-9.7%</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>1726320</t>
+          <t>1726057</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>10.074,94</t>
+          <t>177.769,55</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>59.203,65</t>
+          <t>196.508,79</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>-R$ 49.128,71</t>
+          <t>-R$ 18.739,24</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
@@ -9348,29 +9348,29 @@
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>-83.0%</t>
+          <t>-9.5%</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>1726324</t>
+          <t>1726058</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>2.294,20</t>
+          <t>103.529,88</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>19.215,26</t>
+          <t>133.354,34</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>-R$ 16.921,06</t>
+          <t>-R$ 29.824,46</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
@@ -9380,29 +9380,29 @@
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>-88.1%</t>
+          <t>-22.4%</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>1726332</t>
+          <t>1726318</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>5.722,23</t>
+          <t>17.722,33</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>28.896,74</t>
+          <t>55.391,23</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>-R$ 23.174,51</t>
+          <t>-R$ 37.668,90</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
@@ -9412,29 +9412,29 @@
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>-80.2%</t>
+          <t>-68.0%</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>1726388</t>
+          <t>1726320</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>18.635,34</t>
+          <t>10.074,94</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>41.833,50</t>
+          <t>59.203,65</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>-R$ 23.198,16</t>
+          <t>-R$ 49.128,71</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
@@ -9444,29 +9444,29 @@
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>-55.5%</t>
+          <t>-83.0%</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>1726496</t>
+          <t>1726324</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>24.645,05</t>
+          <t>2.294,20</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>42.100,83</t>
+          <t>19.215,26</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>-R$ 17.455,78</t>
+          <t>-R$ 16.921,06</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
@@ -9476,61 +9476,61 @@
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>-41.5%</t>
+          <t>-88.1%</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>1726541</t>
+          <t>1726332</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>17.173,17</t>
+          <t>5.722,23</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>42,95</t>
+          <t>28.896,74</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>R$ 17.130,22</t>
+          <t>-R$ 23.174,51</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>+39884.1%</t>
+          <t>-80.2%</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>1726890</t>
+          <t>1726388</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>3.252,02</t>
+          <t>18.635,34</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>11.143,51</t>
+          <t>41.833,50</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>-R$ 7.891,49</t>
+          <t>-R$ 23.198,16</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
@@ -9540,61 +9540,61 @@
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>-70.8%</t>
+          <t>-55.5%</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>1727187</t>
+          <t>1726496</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>4.280,60</t>
+          <t>24.645,05</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>42.100,83</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>R$ 4.280,60</t>
+          <t>-R$ 17.455,78</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-41.5%</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>1727287</t>
+          <t>1726541</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>489,21</t>
+          <t>17.173,17</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>42,95</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>R$ 489,21</t>
+          <t>R$ 17.130,22</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
@@ -9604,29 +9604,29 @@
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+39884.1%</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>1727322</t>
+          <t>1726737</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>3.146,66</t>
+          <t>4.070,08</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>11.250,94</t>
+          <t>18.172,61</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>-R$ 8.104,28</t>
+          <t>-R$ 14.102,53</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
@@ -9636,29 +9636,29 @@
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>-72.0%</t>
+          <t>-77.6%</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>1727335</t>
+          <t>1726890</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>5.053,73</t>
+          <t>3.252,02</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>8.079,08</t>
+          <t>11.143,51</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>-R$ 3.025,35</t>
+          <t>-R$ 7.891,49</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
@@ -9668,51 +9668,51 @@
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>-37.4%</t>
+          <t>-70.8%</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>1727529</t>
+          <t>1727187</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>4.366,81</t>
+          <t>4.280,60</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>11.250,94</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>-R$ 6.884,13</t>
+          <t>R$ 4.280,60</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>-61.2%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>1727778</t>
+          <t>1727287</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>3.846,49</t>
+          <t>489,21</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
@@ -9722,7 +9722,7 @@
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>R$ 3.846,49</t>
+          <t>R$ 489,21</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
@@ -9739,54 +9739,54 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>1727808</t>
+          <t>1727322</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>3.146,66</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>11.250,94</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-R$ 8.104,28</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-72.0%</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>1727808I</t>
+          <t>1727335</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>2.562,33</t>
+          <t>5.053,73</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>8.676,98</t>
+          <t>8.079,08</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>-R$ 6.114,65</t>
+          <t>-R$ 3.025,35</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
@@ -9796,29 +9796,29 @@
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>-70.5%</t>
+          <t>-37.4%</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>1727881</t>
+          <t>1727529</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>2.707,35</t>
+          <t>4.366,81</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>2.757,73</t>
+          <t>11.250,94</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>-R$ 50,38</t>
+          <t>-R$ 6.884,13</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
@@ -9828,125 +9828,125 @@
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>-1.8%</t>
+          <t>-61.2%</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>1727882</t>
+          <t>1727778</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>7.415,36</t>
+          <t>3.846,49</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>46.847,53</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>-R$ 39.432,17</t>
+          <t>R$ 3.846,49</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>-84.2%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>1728055</t>
+          <t>1727808</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>12.947,91</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>42.100,83</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>-R$ 29.152,92</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>-69.2%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>1728163</t>
+          <t>1727808I</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>7.914,69</t>
+          <t>2.562,33</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>8.676,98</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>R$ 7.914,69</t>
+          <t>-R$ 6.114,65</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-70.5%</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>1728328</t>
+          <t>1727881</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>3.343,59</t>
+          <t>2.707,35</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>3.565,51</t>
+          <t>2.757,73</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>-R$ 221,92</t>
+          <t>-R$ 50,38</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
@@ -9956,29 +9956,29 @@
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>-6.2%</t>
+          <t>-1.8%</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>1728642</t>
+          <t>1727882</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>7.237,16</t>
+          <t>7.415,36</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>19.215,26</t>
+          <t>46.847,53</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>-R$ 11.978,10</t>
+          <t>-R$ 39.432,17</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
@@ -9988,29 +9988,29 @@
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>-62.3%</t>
+          <t>-84.2%</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>1729300</t>
+          <t>1728055</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>9.521,56</t>
+          <t>12.947,91</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>59.203,65</t>
+          <t>42.100,83</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>-R$ 49.682,09</t>
+          <t>-R$ 29.152,92</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
@@ -10020,93 +10020,93 @@
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>-83.9%</t>
+          <t>-69.2%</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>1729668</t>
+          <t>1728163</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>1.201,81</t>
+          <t>7.914,69</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>13.305,24</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>-R$ 12.103,43</t>
+          <t>R$ 7.914,69</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>-91.0%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>1729786</t>
+          <t>1728328</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>45.387,32</t>
+          <t>3.343,59</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>44.264,28</t>
+          <t>3.565,51</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>R$ 1.123,04</t>
+          <t>-R$ 221,92</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>+2.5%</t>
+          <t>-6.2%</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>1729828</t>
+          <t>1728642</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>914,81</t>
+          <t>7.237,16</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>11.250,94</t>
+          <t>19.215,26</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>-R$ 10.336,13</t>
+          <t>-R$ 11.978,10</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
@@ -10116,29 +10116,29 @@
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>-91.9%</t>
+          <t>-62.3%</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>1730222</t>
+          <t>1729300</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>21.764,18</t>
+          <t>9.521,56</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>28.896,74</t>
+          <t>59.203,65</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>-R$ 7.132,56</t>
+          <t>-R$ 49.682,09</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
@@ -10148,29 +10148,29 @@
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>-24.7%</t>
+          <t>-83.9%</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>1730270</t>
+          <t>1729668</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>10.340,91</t>
+          <t>1.201,81</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>42.100,83</t>
+          <t>13.305,24</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>-R$ 31.759,92</t>
+          <t>-R$ 12.103,43</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
@@ -10180,61 +10180,61 @@
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>-75.4%</t>
+          <t>-91.0%</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>1730313</t>
+          <t>1729786</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>2.885,97</t>
+          <t>45.387,32</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>113.288,94</t>
+          <t>44.264,28</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>-R$ 110.402,97</t>
+          <t>R$ 1.123,04</t>
         </is>
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>-97.5%</t>
+          <t>+2.5%</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>1730642I</t>
+          <t>1729828</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>15.899,82</t>
+          <t>914,81</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>20.657,21</t>
+          <t>11.250,94</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>-R$ 4.757,39</t>
+          <t>-R$ 10.336,13</t>
         </is>
       </c>
       <c r="E307" t="inlineStr">
@@ -10244,29 +10244,29 @@
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>-23.0%</t>
+          <t>-91.9%</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>1730707</t>
+          <t>1730222</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>7.655,46</t>
+          <t>21.764,18</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>46.847,53</t>
+          <t>28.896,74</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>-R$ 39.192,07</t>
+          <t>-R$ 7.132,56</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">
@@ -10276,29 +10276,29 @@
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>-83.7%</t>
+          <t>-24.7%</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>1730763</t>
+          <t>1730270</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>4.973,33</t>
+          <t>10.340,91</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>59.203,65</t>
+          <t>42.100,83</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>-R$ 54.230,32</t>
+          <t>-R$ 31.759,92</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
@@ -10308,29 +10308,29 @@
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>-91.6%</t>
+          <t>-75.4%</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>1730822</t>
+          <t>1730313</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>31.373,82</t>
+          <t>2.885,97</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>68.930,71</t>
+          <t>113.288,94</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>-R$ 37.556,89</t>
+          <t>-R$ 110.402,97</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">
@@ -10340,29 +10340,29 @@
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>-54.5%</t>
+          <t>-97.5%</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>1730908</t>
+          <t>1730642I</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>4.386,39</t>
+          <t>15.899,82</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>17.270,31</t>
+          <t>20.657,21</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>-R$ 12.883,92</t>
+          <t>-R$ 4.757,39</t>
         </is>
       </c>
       <c r="E311" t="inlineStr">
@@ -10372,285 +10372,285 @@
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>-74.6%</t>
+          <t>-23.0%</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>1731653</t>
+          <t>1730707</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>5.940,43</t>
+          <t>7.655,46</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>46.847,53</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>R$ 5.940,43</t>
+          <t>-R$ 39.192,07</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-83.7%</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>1731746</t>
+          <t>1730763</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>1.571,63</t>
+          <t>4.973,33</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>1.571,60</t>
+          <t>59.203,65</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>R$ 0,03</t>
+          <t>-R$ 54.230,32</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>+0.0%</t>
+          <t>-91.6%</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>1732157</t>
+          <t>1730822</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>3.748,66</t>
+          <t>31.373,82</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>3.356,46</t>
+          <t>68.930,71</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>R$ 392,20</t>
+          <t>-R$ 37.556,89</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>+11.7%</t>
+          <t>-54.5%</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>1733419I</t>
+          <t>1730908</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>1.171,48</t>
+          <t>4.386,39</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>1.085,22</t>
+          <t>17.270,31</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>R$ 86,26</t>
+          <t>-R$ 12.883,92</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>+7.9%</t>
+          <t>-74.6%</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>1734449</t>
+          <t>1731653</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>10.662,83</t>
+          <t>5.940,43</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>46.847,53</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>-R$ 36.184,70</t>
+          <t>R$ 5.940,43</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>-77.2%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>1734835I</t>
+          <t>1731746</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>16.200,62</t>
+          <t>1.571,63</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>17.293,31</t>
+          <t>1.571,60</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>-R$ 1.092,69</t>
+          <t>R$ 0,03</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>-6.3%</t>
+          <t>+0.0%</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>1737272</t>
+          <t>1732157</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>4.617,63</t>
+          <t>3.748,66</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>11.970,80</t>
+          <t>3.356,46</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>-R$ 7.353,17</t>
+          <t>R$ 392,20</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>-61.4%</t>
+          <t>+11.7%</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>1737274</t>
+          <t>1733419I</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>4.617,63</t>
+          <t>1.171,48</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>11.167,26</t>
+          <t>1.085,22</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>-R$ 6.549,63</t>
+          <t>R$ 86,26</t>
         </is>
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>-58.7%</t>
+          <t>+7.9%</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>1737280</t>
+          <t>1734449</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>2.886,03</t>
+          <t>10.662,83</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>45.915,63</t>
+          <t>46.847,53</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>-R$ 43.029,60</t>
+          <t>-R$ 36.184,70</t>
         </is>
       </c>
       <c r="E320" t="inlineStr">
@@ -10660,29 +10660,29 @@
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>-93.7%</t>
+          <t>-77.2%</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>1737483</t>
+          <t>1734835I</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>5.194,82</t>
+          <t>16.200,62</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>25.279,27</t>
+          <t>17.293,31</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>-R$ 20.084,45</t>
+          <t>-R$ 1.092,69</t>
         </is>
       </c>
       <c r="E321" t="inlineStr">
@@ -10692,29 +10692,29 @@
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>-79.5%</t>
+          <t>-6.3%</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>1737484</t>
+          <t>1737272</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>5.194,82</t>
+          <t>4.617,63</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>25.279,27</t>
+          <t>11.970,80</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>-R$ 20.084,45</t>
+          <t>-R$ 7.353,17</t>
         </is>
       </c>
       <c r="E322" t="inlineStr">
@@ -10724,14 +10724,14 @@
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>-79.5%</t>
+          <t>-61.4%</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>1740643</t>
+          <t>1737274</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
@@ -10741,12 +10741,12 @@
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>113.288,94</t>
+          <t>11.167,26</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>-R$ 108.671,31</t>
+          <t>-R$ 6.549,63</t>
         </is>
       </c>
       <c r="E323" t="inlineStr">
@@ -10756,29 +10756,29 @@
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>-95.9%</t>
+          <t>-58.7%</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>1741124</t>
+          <t>1737280</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>2.885,97</t>
+          <t>2.886,03</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>113.288,94</t>
+          <t>45.915,63</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>-R$ 110.402,97</t>
+          <t>-R$ 43.029,60</t>
         </is>
       </c>
       <c r="E324" t="inlineStr">
@@ -10788,37 +10788,165 @@
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>-97.5%</t>
+          <t>-93.7%</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
+          <t>1737483</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>5.194,82</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>25.279,27</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>-R$ 20.084,45</t>
+        </is>
+      </c>
+      <c r="E325" t="inlineStr">
+        <is>
+          <t>❌ PREJUÍZO</t>
+        </is>
+      </c>
+      <c r="F325" t="inlineStr">
+        <is>
+          <t>-79.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>1737484</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>5.194,82</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>25.279,27</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>-R$ 20.084,45</t>
+        </is>
+      </c>
+      <c r="E326" t="inlineStr">
+        <is>
+          <t>❌ PREJUÍZO</t>
+        </is>
+      </c>
+      <c r="F326" t="inlineStr">
+        <is>
+          <t>-79.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>1740643</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>4.617,63</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>113.288,94</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>-R$ 108.671,31</t>
+        </is>
+      </c>
+      <c r="E327" t="inlineStr">
+        <is>
+          <t>❌ PREJUÍZO</t>
+        </is>
+      </c>
+      <c r="F327" t="inlineStr">
+        <is>
+          <t>-95.9%</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>1741124</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>2.885,97</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>113.288,94</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>-R$ 110.402,97</t>
+        </is>
+      </c>
+      <c r="E328" t="inlineStr">
+        <is>
+          <t>❌ PREJUÍZO</t>
+        </is>
+      </c>
+      <c r="F328" t="inlineStr">
+        <is>
+          <t>-97.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
           <t>1741248</t>
         </is>
       </c>
-      <c r="B325" t="inlineStr">
+      <c r="B329" t="inlineStr">
         <is>
           <t>4.617,63</t>
         </is>
       </c>
-      <c r="C325" t="inlineStr">
+      <c r="C329" t="inlineStr">
         <is>
           <t>113.288,94</t>
         </is>
       </c>
-      <c r="D325" t="inlineStr">
+      <c r="D329" t="inlineStr">
         <is>
           <t>-R$ 108.671,31</t>
         </is>
       </c>
-      <c r="E325" t="inlineStr">
-        <is>
-          <t>❌ PREJUÍZO</t>
-        </is>
-      </c>
-      <c r="F325" t="inlineStr">
+      <c r="E329" t="inlineStr">
+        <is>
+          <t>❌ PREJUÍZO</t>
+        </is>
+      </c>
+      <c r="F329" t="inlineStr">
         <is>
           <t>-95.9%</t>
         </is>

--- a/analise_financeira.xlsx
+++ b/analise_financeira.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F329"/>
+  <dimension ref="A1:F332"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1547,54 +1547,54 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>1674093</t>
+          <t>1671216C</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>4.813,55</t>
+          <t>13,51</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>13.305,24</t>
+          <t>13,48</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>-R$ 8.491,69</t>
+          <t>R$ 0,03</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>-63.8%</t>
+          <t>+0.2%</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>1675032C</t>
+          <t>1671216I</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>23,99</t>
+          <t>8.907,02</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>8.880,62</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>R$ 23,99</t>
+          <t>R$ 26,40</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1604,51 +1604,51 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.3%</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>1675032I</t>
+          <t>1674093</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>222.884,15</t>
+          <t>4.813,55</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>13.305,24</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>R$ 222.884,15</t>
+          <t>-R$ 8.491,69</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-63.8%</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>1675389</t>
+          <t>1675032C</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>389,52</t>
+          <t>23,99</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>R$ 389,52</t>
+          <t>R$ 23,99</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1675,12 +1675,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>1676605</t>
+          <t>1675032I</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>127.656,50</t>
+          <t>222.884,15</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1690,7 +1690,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>R$ 127.656,50</t>
+          <t>R$ 222.884,15</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1707,22 +1707,22 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>1677314</t>
+          <t>1675389</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>51.640,54</t>
+          <t>389,52</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>139,89</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>R$ 51.500,65</t>
+          <t>R$ 389,52</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1732,29 +1732,29 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>+36815.1%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>1677316</t>
+          <t>1676605</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>51.623,62</t>
+          <t>127.656,50</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>139,89</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>R$ 51.483,73</t>
+          <t>R$ 127.656,50</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -1764,29 +1764,29 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>+36803.0%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>1682195</t>
+          <t>1677314</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>8,36</t>
+          <t>51.640,54</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>139,89</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>R$ 8,36</t>
+          <t>R$ 51.500,65</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -1796,29 +1796,29 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+36815.1%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>1683861I</t>
+          <t>1677316</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>20.224,44</t>
+          <t>51.623,62</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>139,89</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>R$ 20.224,44</t>
+          <t>R$ 51.483,73</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -1828,19 +1828,19 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+36803.0%</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>1686607C</t>
+          <t>1682195</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>21,97</t>
+          <t>8,36</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>R$ 21,97</t>
+          <t>R$ 8,36</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -1867,12 +1867,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>1686607I</t>
+          <t>1683861I</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>1.195,62</t>
+          <t>20.224,44</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1882,7 +1882,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>R$ 1.195,62</t>
+          <t>R$ 20.224,44</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -1899,76 +1899,76 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>1687268</t>
+          <t>1686607C</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>29.041,79</t>
+          <t>21,97</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>377.992,56</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>-R$ 348.950,77</t>
+          <t>R$ 21,97</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>-92.3%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>1687274</t>
+          <t>1686607I</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>44.404,89</t>
+          <t>1.195,62</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>377.992,56</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>-R$ 333.587,67</t>
+          <t>R$ 1.195,62</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>-88.3%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>1687276</t>
+          <t>1687268</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>68.131,64</t>
+          <t>29.041,79</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1978,7 +1978,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>-R$ 309.860,92</t>
+          <t>-R$ 348.950,77</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -1988,19 +1988,19 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>-82.0%</t>
+          <t>-92.3%</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>1687278</t>
+          <t>1687274</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>76.729,20</t>
+          <t>44.404,89</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2010,7 +2010,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>-R$ 301.263,36</t>
+          <t>-R$ 333.587,67</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -2020,19 +2020,19 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>-79.7%</t>
+          <t>-88.3%</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>1687282</t>
+          <t>1687276</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>72.244,67</t>
+          <t>68.131,64</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2042,7 +2042,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>-R$ 305.747,89</t>
+          <t>-R$ 309.860,92</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -2052,19 +2052,19 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>-80.9%</t>
+          <t>-82.0%</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>1687285</t>
+          <t>1687278</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>50.037,23</t>
+          <t>76.729,20</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2074,7 +2074,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>-R$ 327.955,33</t>
+          <t>-R$ 301.263,36</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -2084,211 +2084,211 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>-86.8%</t>
+          <t>-79.7%</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>1688115C</t>
+          <t>1687282</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>13,01</t>
+          <t>72.244,67</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>377.992,56</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>R$ 13,01</t>
+          <t>-R$ 305.747,89</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-80.9%</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>1688115I</t>
+          <t>1687285</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>21.423,48</t>
+          <t>50.037,23</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>377.992,56</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>R$ 21.423,48</t>
+          <t>-R$ 327.955,33</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-86.8%</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>1689263</t>
+          <t>1688115C</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>4.336,11</t>
+          <t>13,01</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>15.265,20</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>-R$ 10.929,09</t>
+          <t>R$ 13,01</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>-71.6%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>1689264</t>
+          <t>1688115I</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>10.986,17</t>
+          <t>21.423,48</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>15.265,20</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>-R$ 4.279,03</t>
+          <t>R$ 21.423,48</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>-28.0%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>1691380</t>
+          <t>1689263</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>4.336,11</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>15.265,20</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-R$ 10.929,09</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-71.6%</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>1691390</t>
+          <t>1689264</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>457,30</t>
+          <t>10.986,17</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>15.265,20</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>R$ 457,30</t>
+          <t>-R$ 4.279,03</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-28.0%</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>1691534</t>
+          <t>1691380</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>21.331,31</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2298,12 +2298,12 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>R$ 21.331,31</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2315,12 +2315,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>1692174</t>
+          <t>1691390</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>457,30</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2330,12 +2330,12 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 457,30</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2347,12 +2347,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>1692415</t>
+          <t>1691534</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>4.712,56</t>
+          <t>21.331,31</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2362,7 +2362,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>R$ 4.712,56</t>
+          <t>R$ 21.331,31</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -2379,12 +2379,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>1692636</t>
+          <t>1692174</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>19.387,05</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2394,12 +2394,12 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>R$ 19.387,05</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2411,12 +2411,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>1693027</t>
+          <t>1692415</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2.215,91</t>
+          <t>4.712,56</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2426,7 +2426,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>R$ 2.215,91</t>
+          <t>R$ 4.712,56</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -2443,12 +2443,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>1694202</t>
+          <t>1692636</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>4.490,43</t>
+          <t>19.387,05</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2458,7 +2458,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>R$ 4.490,43</t>
+          <t>R$ 19.387,05</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -2475,12 +2475,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>1694258</t>
+          <t>1693027</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>127.751,38</t>
+          <t>2.215,91</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2490,7 +2490,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>R$ 127.751,38</t>
+          <t>R$ 2.215,91</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -2507,12 +2507,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>1694264</t>
+          <t>1694202</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>4.490,43</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 4.490,43</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2539,44 +2539,44 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>1694841</t>
+          <t>1694258</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>5.640,24</t>
+          <t>127.751,38</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>25.002,10</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>-R$ 19.361,86</t>
+          <t>R$ 127.751,38</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>-77.4%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>1694861</t>
+          <t>1694264</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>3.068,09</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2586,12 +2586,12 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>R$ 3.068,09</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2603,44 +2603,44 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>1695716</t>
+          <t>1694841</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>87.362,74</t>
+          <t>5.640,24</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>25.002,10</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>R$ 87.362,74</t>
+          <t>-R$ 19.361,86</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-77.4%</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>1697210</t>
+          <t>1694861</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>12.986,17</t>
+          <t>3.068,09</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2650,7 +2650,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>R$ 12.986,17</t>
+          <t>R$ 3.068,09</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -2667,12 +2667,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>1697210I</t>
+          <t>1695716</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>12.986,17</t>
+          <t>87.362,74</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2682,7 +2682,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>R$ 12.986,17</t>
+          <t>R$ 87.362,74</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -2699,44 +2699,44 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>1697912</t>
+          <t>1697210</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>1.318,82</t>
+          <t>12.986,17</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>13.305,24</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>-R$ 11.986,42</t>
+          <t>R$ 12.986,17</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>-90.1%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>1698047</t>
+          <t>1697210I</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2.449,89</t>
+          <t>12.986,17</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>R$ 2.449,89</t>
+          <t>R$ 12.986,17</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -2763,44 +2763,44 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>1698056</t>
+          <t>1697912</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>9.658,39</t>
+          <t>1.318,82</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>7.099,38</t>
+          <t>13.305,24</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>R$ 2.559,01</t>
+          <t>-R$ 11.986,42</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>+36.0%</t>
+          <t>-90.1%</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>1698781</t>
+          <t>1698047</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>914,56</t>
+          <t>2.449,89</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>R$ 914,56</t>
+          <t>R$ 2.449,89</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -2827,44 +2827,44 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>1699516</t>
+          <t>1698056</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>3.676,47</t>
+          <t>9.658,39</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>30.150,78</t>
+          <t>7.099,38</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>-R$ 26.474,31</t>
+          <t>R$ 2.559,01</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>-87.8%</t>
+          <t>+36.0%</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>1700852</t>
+          <t>1698781</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>12.509,24</t>
+          <t>914,56</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2874,7 +2874,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>R$ 12.509,24</t>
+          <t>R$ 914,56</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -2891,44 +2891,44 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>1702127</t>
+          <t>1699516</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>3.676,47</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>30.150,78</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-R$ 26.474,31</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-87.8%</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>1702212</t>
+          <t>1700852</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>9.859,97</t>
+          <t>12.509,24</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -2938,7 +2938,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>R$ 9.859,97</t>
+          <t>R$ 12.509,24</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -2955,12 +2955,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>1702640</t>
+          <t>1702127</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2.963,92</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -2970,12 +2970,12 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>R$ 2.963,92</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -2987,12 +2987,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>1702776C</t>
+          <t>1702212</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>9.859,97</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -3002,12 +3002,12 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 9.859,97</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3019,12 +3019,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>1702776I</t>
+          <t>1702640</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>18.098,87</t>
+          <t>2.963,92</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -3034,7 +3034,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>R$ 18.098,87</t>
+          <t>R$ 2.963,92</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -3051,12 +3051,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>1703223</t>
+          <t>1702776C</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>19.640,49</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -3066,12 +3066,12 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>R$ 19.640,49</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3083,44 +3083,44 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>1704074</t>
+          <t>1702776I</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>54.055,77</t>
+          <t>18.098,87</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>70.485,69</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>-R$ 16.429,92</t>
+          <t>R$ 18.098,87</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>-23.3%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>1704476</t>
+          <t>1703223</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>31.763,92</t>
+          <t>19.640,49</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -3130,7 +3130,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>R$ 31.763,92</t>
+          <t>R$ 19.640,49</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -3147,44 +3147,44 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>1704477</t>
+          <t>1704074</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>26.586,40</t>
+          <t>54.055,77</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>70.485,69</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>R$ 26.586,40</t>
+          <t>-R$ 16.429,92</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-23.3%</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>1704525</t>
+          <t>1704476</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>15.452,25</t>
+          <t>31.763,92</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3194,7 +3194,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>R$ 15.452,25</t>
+          <t>R$ 31.763,92</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -3211,118 +3211,118 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>1704802</t>
+          <t>1704477</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>6.266,64</t>
+          <t>26.586,40</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>59.203,65</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>-R$ 52.937,01</t>
+          <t>R$ 26.586,40</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>-89.4%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>1704855</t>
+          <t>1704525</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>92.191,04</t>
+          <t>15.452,25</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>205.265,15</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>-R$ 113.074,11</t>
+          <t>R$ 15.452,25</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>-55.1%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>1704867</t>
+          <t>1704802</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>23.915,48</t>
+          <t>6.266,64</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>59.203,65</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>R$ 23.915,48</t>
+          <t>-R$ 52.937,01</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-89.4%</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>1704877</t>
+          <t>1704855</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>159.866,42</t>
+          <t>92.191,04</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>164.923,77</t>
+          <t>205.265,15</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>-R$ 5.057,35</t>
+          <t>-R$ 113.074,11</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -3332,29 +3332,29 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>-3.1%</t>
+          <t>-55.1%</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>1704891</t>
+          <t>1704867</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>178.087,99</t>
+          <t>23.915,48</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>163.376,34</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>R$ 14.711,65</t>
+          <t>R$ 23.915,48</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -3364,29 +3364,29 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>+9.0%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>1704920</t>
+          <t>1704877</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>58.137,43</t>
+          <t>159.866,42</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>132.320,57</t>
+          <t>164.923,77</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>-R$ 74.183,14</t>
+          <t>-R$ 5.057,35</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -3396,29 +3396,29 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>-56.1%</t>
+          <t>-3.1%</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>1704952</t>
+          <t>1704891</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>1.289,24</t>
+          <t>178.087,99</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>163.376,34</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>R$ 1.289,24</t>
+          <t>R$ 14.711,65</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -3428,51 +3428,51 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+9.0%</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>1704953</t>
+          <t>1704920</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>9.260,98</t>
+          <t>58.137,43</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>132.320,57</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>R$ 9.260,98</t>
+          <t>-R$ 74.183,14</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-56.1%</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>1704964</t>
+          <t>1704952</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>2.692,23</t>
+          <t>1.289,24</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3482,7 +3482,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>R$ 2.692,23</t>
+          <t>R$ 1.289,24</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -3499,12 +3499,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>1704968</t>
+          <t>1704953</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>2.808,15</t>
+          <t>9.260,98</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>R$ 2.808,15</t>
+          <t>R$ 9.260,98</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -3531,12 +3531,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>1705034</t>
+          <t>1704964</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>28.171,03</t>
+          <t>2.692,23</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3546,7 +3546,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>R$ 28.171,03</t>
+          <t>R$ 2.692,23</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -3563,44 +3563,44 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>1705074</t>
+          <t>1704968</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>150.312,87</t>
+          <t>2.808,15</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>382.282,74</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>-R$ 231.969,87</t>
+          <t>R$ 2.808,15</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>-60.7%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>1705802I</t>
+          <t>1705034</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>28.171,03</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 28.171,03</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3627,76 +3627,76 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>1706284</t>
+          <t>1705074</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>2.060,27</t>
+          <t>150.312,87</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>382.282,74</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>R$ 2.060,27</t>
+          <t>-R$ 231.969,87</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-60.7%</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>1706327</t>
+          <t>1705802I</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>162.240,34</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>228.421,85</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>-R$ 66.181,51</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>-29.0%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>1707174</t>
+          <t>1706284</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>1.924,94</t>
+          <t>2.060,27</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>R$ 1.924,94</t>
+          <t>R$ 2.060,27</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -3723,118 +3723,118 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>1707182</t>
+          <t>1706327</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>99.018,80</t>
+          <t>162.240,34</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>228.421,85</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>R$ 99.018,80</t>
+          <t>-R$ 66.181,51</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-29.0%</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>1707502</t>
+          <t>1707174</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>3.133,81</t>
+          <t>1.924,94</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>37.895,39</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>-R$ 34.761,58</t>
+          <t>R$ 1.924,94</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>-91.7%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>1707510</t>
+          <t>1707182</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>11.962,34</t>
+          <t>99.018,80</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>37.895,39</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>-R$ 25.933,05</t>
+          <t>R$ 99.018,80</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>-68.4%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>1707817</t>
+          <t>1707502</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>138.680,75</t>
+          <t>3.133,81</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>382.282,74</t>
+          <t>37.895,39</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>-R$ 243.601,99</t>
+          <t>-R$ 34.761,58</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -3844,83 +3844,83 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>-63.7%</t>
+          <t>-91.7%</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>1708066</t>
+          <t>1707510</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>3.419,06</t>
+          <t>11.962,34</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>37.895,39</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>R$ 3.419,06</t>
+          <t>-R$ 25.933,05</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-68.4%</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>1708877</t>
+          <t>1707817</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>3,54</t>
+          <t>138.680,75</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>382.282,74</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>R$ 3,54</t>
+          <t>-R$ 243.601,99</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-63.7%</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>1708877I</t>
+          <t>1708066</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>2.132,72</t>
+          <t>3.419,06</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -3930,7 +3930,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>R$ 2.132,72</t>
+          <t>R$ 3.419,06</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -3947,12 +3947,12 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>1708906</t>
+          <t>1708877</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>7.652,25</t>
+          <t>3,54</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -3962,7 +3962,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>R$ 7.652,25</t>
+          <t>R$ 3,54</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -3979,22 +3979,22 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>1708908</t>
+          <t>1708877I</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>34.163,18</t>
+          <t>2.132,72</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>29.400,43</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>R$ 4.762,75</t>
+          <t>R$ 2.132,72</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -4004,19 +4004,19 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>+16.2%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>1709419</t>
+          <t>1708906</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>7.652,25</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -4026,12 +4026,12 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 7.652,25</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4043,44 +4043,44 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>1709486</t>
+          <t>1708908</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>6.291,40</t>
+          <t>34.163,18</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>47.063,85</t>
+          <t>29.400,43</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>-R$ 40.772,45</t>
+          <t>R$ 4.762,75</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>-86.6%</t>
+          <t>+16.2%</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>1709995</t>
+          <t>1709419</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>2.410,16</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>R$ 2.410,16</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4107,54 +4107,54 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>1710116</t>
+          <t>1709486</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>6.291,40</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>47.063,85</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-R$ 40.772,45</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-86.6%</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>1710220</t>
+          <t>1709995</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>2.270,95</t>
+          <t>2.410,16</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>2.270,94</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>R$ 0,01</t>
+          <t>R$ 2.410,16</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -4164,19 +4164,19 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>+0.0%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>1710287C</t>
+          <t>1710116</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>56,80</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -4186,12 +4186,12 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>R$ 56,80</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4203,22 +4203,22 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>1710287I</t>
+          <t>1710220</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>8.740,43</t>
+          <t>2.270,95</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>2.270,94</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>R$ 8.740,43</t>
+          <t>R$ 0,01</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -4228,29 +4228,29 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.0%</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>1710322</t>
+          <t>1710287C</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>190.028,30</t>
+          <t>56,80</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>176.859,43</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>R$ 13.168,87</t>
+          <t>R$ 56,80</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -4260,19 +4260,19 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>+7.4%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>1710329</t>
+          <t>1710287I</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>24.211,86</t>
+          <t>8.740,43</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -4282,7 +4282,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>R$ 24.211,86</t>
+          <t>R$ 8.740,43</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -4299,22 +4299,22 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>1710332</t>
+          <t>1710322</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>223,64</t>
+          <t>190.028,30</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>176.859,43</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>R$ 223,64</t>
+          <t>R$ 13.168,87</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -4324,19 +4324,19 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+7.4%</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>1710735</t>
+          <t>1710329</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>9.751,61</t>
+          <t>24.211,86</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>R$ 9.751,61</t>
+          <t>R$ 24.211,86</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -4363,12 +4363,12 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>1710736</t>
+          <t>1710332</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>223,64</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -4378,12 +4378,12 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 223,64</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4395,12 +4395,12 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>1710937</t>
+          <t>1710735</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>4.234,81</t>
+          <t>9.751,61</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -4410,7 +4410,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>R$ 4.234,81</t>
+          <t>R$ 9.751,61</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -4427,12 +4427,12 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>1710975</t>
+          <t>1710736</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>913,41</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -4442,12 +4442,12 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>R$ 913,41</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4459,12 +4459,12 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>1711110</t>
+          <t>1710937</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>4.234,81</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -4474,12 +4474,12 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 4.234,81</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4491,44 +4491,44 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>1711378</t>
+          <t>1710975</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>9.934,10</t>
+          <t>913,41</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>10.727,58</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>-R$ 793,48</t>
+          <t>R$ 913,41</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>-7.4%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>1711384</t>
+          <t>1711110</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>2.250,33</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -4538,12 +4538,12 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>R$ 2.250,33</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -4555,86 +4555,86 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>1711454</t>
+          <t>1711378</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>10.429,60</t>
+          <t>9.934,10</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>10.727,58</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>R$ 10.429,60</t>
+          <t>-R$ 793,48</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-7.4%</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>1711489</t>
+          <t>1711384</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>4.381,49</t>
+          <t>2.250,33</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>73.801,59</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>-R$ 69.420,10</t>
+          <t>R$ 2.250,33</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>-94.1%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>1711507</t>
+          <t>1711454</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>15.939,34</t>
+          <t>10.429,60</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>13.503,20</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>R$ 2.436,14</t>
+          <t>R$ 10.429,60</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -4644,115 +4644,115 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>+18.0%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>1711525</t>
+          <t>1711489</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>2.125,35</t>
+          <t>4.381,49</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>73.801,59</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>R$ 2.125,35</t>
+          <t>-R$ 69.420,10</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-94.1%</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>1711629</t>
+          <t>1711507</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>4.201,07</t>
+          <t>15.939,34</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>13.482,28</t>
+          <t>13.503,20</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>-R$ 9.281,21</t>
+          <t>R$ 2.436,14</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>-68.8%</t>
+          <t>+18.0%</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>1711775</t>
+          <t>1711525</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>1.932,93</t>
+          <t>2.125,35</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>2.356,20</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>-R$ 423,27</t>
+          <t>R$ 2.125,35</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>-18.0%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>1711788</t>
+          <t>1711629</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>8.104,03</t>
+          <t>4.201,07</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -4762,7 +4762,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>-R$ 5.378,25</t>
+          <t>-R$ 9.281,21</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -4772,83 +4772,83 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>-39.9%</t>
+          <t>-68.8%</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>1712530</t>
+          <t>1711775</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>6.922,75</t>
+          <t>1.932,93</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>2.356,20</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>R$ 6.922,75</t>
+          <t>-R$ 423,27</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-18.0%</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>1712531</t>
+          <t>1711788</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>5.019,99</t>
+          <t>8.104,03</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>13.482,28</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>R$ 5.019,99</t>
+          <t>-R$ 5.378,25</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-39.9%</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>1712533</t>
+          <t>1712530</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>2.680,86</t>
+          <t>6.922,75</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -4858,7 +4858,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>R$ 2.680,86</t>
+          <t>R$ 6.922,75</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -4875,12 +4875,12 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>1712538</t>
+          <t>1712531</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>3.955,41</t>
+          <t>5.019,99</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>R$ 3.955,41</t>
+          <t>R$ 5.019,99</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -4907,12 +4907,12 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>1712547</t>
+          <t>1712533</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>7.069,45</t>
+          <t>2.680,86</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -4922,7 +4922,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>R$ 7.069,45</t>
+          <t>R$ 2.680,86</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -4939,12 +4939,12 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>1712550</t>
+          <t>1712538</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>5.007,08</t>
+          <t>3.955,41</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -4954,7 +4954,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>R$ 5.007,08</t>
+          <t>R$ 3.955,41</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -4971,12 +4971,12 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>1712624</t>
+          <t>1712547</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>3.073,90</t>
+          <t>7.069,45</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -4986,7 +4986,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>R$ 3.073,90</t>
+          <t>R$ 7.069,45</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -5003,12 +5003,12 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>1712766</t>
+          <t>1712550</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>705,45</t>
+          <t>5.007,08</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>R$ 705,45</t>
+          <t>R$ 5.007,08</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -5035,12 +5035,12 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>1712957</t>
+          <t>1712624</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>2.222,83</t>
+          <t>3.073,90</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -5050,7 +5050,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>R$ 2.222,83</t>
+          <t>R$ 3.073,90</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -5067,12 +5067,12 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>1712963I</t>
+          <t>1712766</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>12.285,61</t>
+          <t>705,45</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -5082,7 +5082,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>R$ 12.285,61</t>
+          <t>R$ 705,45</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -5099,12 +5099,12 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>1713044C</t>
+          <t>1712957</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>21,11</t>
+          <t>2.222,83</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -5114,7 +5114,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>R$ 21,11</t>
+          <t>R$ 2.222,83</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -5131,12 +5131,12 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>1713044I</t>
+          <t>1712963I</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>1.528,53</t>
+          <t>12.285,61</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -5146,7 +5146,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>R$ 1.528,53</t>
+          <t>R$ 12.285,61</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -5163,44 +5163,44 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>1713045</t>
+          <t>1713044C</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>29.639,83</t>
+          <t>21,11</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>205.265,15</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>-R$ 175.625,32</t>
+          <t>R$ 21,11</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>-85.6%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>1713221</t>
+          <t>1713044I</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>18.794,09</t>
+          <t>1.528,53</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -5210,7 +5210,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>R$ 18.794,09</t>
+          <t>R$ 1.528,53</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -5227,44 +5227,44 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>1713223</t>
+          <t>1713045</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>13.438,83</t>
+          <t>29.639,83</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>205.265,15</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>R$ 13.438,83</t>
+          <t>-R$ 175.625,32</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-85.6%</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>1713226</t>
+          <t>1713221</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>3.287,04</t>
+          <t>18.794,09</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -5274,7 +5274,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>R$ 3.287,04</t>
+          <t>R$ 18.794,09</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -5291,12 +5291,12 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>1713240</t>
+          <t>1713223</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>5.108,11</t>
+          <t>13.438,83</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -5306,7 +5306,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>R$ 5.108,11</t>
+          <t>R$ 13.438,83</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -5323,44 +5323,44 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>1713260</t>
+          <t>1713226</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>10.803,62</t>
+          <t>3.287,04</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>73.801,59</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>-R$ 62.997,97</t>
+          <t>R$ 3.287,04</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>-85.4%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>1713262</t>
+          <t>1713240</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>2.675,61</t>
+          <t>5.108,11</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -5370,7 +5370,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>R$ 2.675,61</t>
+          <t>R$ 5.108,11</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -5387,44 +5387,44 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>1713351</t>
+          <t>1713260</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>622,97</t>
+          <t>10.803,62</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>73.801,59</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>R$ 622,97</t>
+          <t>-R$ 62.997,97</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-85.4%</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>1713435I</t>
+          <t>1713262</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>2.675,61</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -5434,12 +5434,12 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 2.675,61</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -5451,12 +5451,12 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>1713626</t>
+          <t>1713351</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>161,42</t>
+          <t>622,97</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -5466,7 +5466,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>R$ 161,42</t>
+          <t>R$ 622,97</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -5483,12 +5483,12 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>1713626I</t>
+          <t>1713435I</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>5.318,80</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>R$ 5.318,80</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -5515,12 +5515,12 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>1713656</t>
+          <t>1713626</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>4.315,58</t>
+          <t>161,42</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -5530,7 +5530,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>R$ 4.315,58</t>
+          <t>R$ 161,42</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -5547,12 +5547,12 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>1713656I</t>
+          <t>1713626I</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>161,74</t>
+          <t>5.318,80</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -5562,7 +5562,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>R$ 161,74</t>
+          <t>R$ 5.318,80</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -5579,12 +5579,12 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>1713660</t>
+          <t>1713656</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>161,11</t>
+          <t>4.315,58</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -5594,7 +5594,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>R$ 161,11</t>
+          <t>R$ 4.315,58</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -5611,12 +5611,12 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>1713679</t>
+          <t>1713656I</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>3.574,44</t>
+          <t>161,74</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -5626,7 +5626,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>R$ 3.574,44</t>
+          <t>R$ 161,74</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -5643,44 +5643,44 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>1713681</t>
+          <t>1713660</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>1.473,94</t>
+          <t>161,11</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>13.482,28</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>-R$ 12.008,34</t>
+          <t>R$ 161,11</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>-89.1%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>1713719</t>
+          <t>1713679</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>3.385,92</t>
+          <t>3.574,44</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -5690,7 +5690,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>R$ 3.385,92</t>
+          <t>R$ 3.574,44</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -5707,44 +5707,44 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>1713903C</t>
+          <t>1713681</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>36,14</t>
+          <t>1.473,94</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>13.482,28</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>R$ 36,14</t>
+          <t>-R$ 12.008,34</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-89.1%</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>1713903I</t>
+          <t>1713719</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>972,91</t>
+          <t>3.385,92</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -5754,7 +5754,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>R$ 972,91</t>
+          <t>R$ 3.385,92</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -5771,12 +5771,12 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>1713916</t>
+          <t>1713903C</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>4.815,09</t>
+          <t>36,14</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -5786,7 +5786,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>R$ 4.815,09</t>
+          <t>R$ 36,14</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -5803,12 +5803,12 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>1713933</t>
+          <t>1713903I</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>5.530,92</t>
+          <t>972,91</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -5818,7 +5818,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>R$ 5.530,92</t>
+          <t>R$ 972,91</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -5835,54 +5835,54 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>1714342</t>
+          <t>1713916</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>2.011,96</t>
+          <t>7.898,27</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>22.187,97</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>-R$ 20.176,01</t>
+          <t>R$ 7.898,27</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>-90.9%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>1714348</t>
+          <t>1713933</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>8.422,88</t>
+          <t>5.530,92</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>6.874,07</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>R$ 1.548,81</t>
+          <t>R$ 5.530,92</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
@@ -5892,83 +5892,83 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>+22.5%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>1714364</t>
+          <t>1714342</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>54,64</t>
+          <t>2.011,96</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>22.187,97</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>R$ 54,64</t>
+          <t>-R$ 20.176,01</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-90.9%</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>1714699</t>
+          <t>1714348</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>25.018,29</t>
+          <t>8.422,88</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>55.022,87</t>
+          <t>6.874,07</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>-R$ 30.004,58</t>
+          <t>R$ 1.548,81</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>-54.5%</t>
+          <t>+22.5%</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>1714729</t>
+          <t>1714364</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>6.722,61</t>
+          <t>54,64</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -5978,7 +5978,7 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>R$ 6.722,61</t>
+          <t>R$ 54,64</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
@@ -5995,44 +5995,44 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>1714857</t>
+          <t>1714699</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>185,07</t>
+          <t>25.018,29</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>55.022,87</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>R$ 185,07</t>
+          <t>-R$ 30.004,58</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-54.5%</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>1714909</t>
+          <t>1714729</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>1.062,57</t>
+          <t>6.722,61</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -6042,7 +6042,7 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>R$ 1.062,57</t>
+          <t>R$ 6.722,61</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
@@ -6059,12 +6059,12 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>1715127</t>
+          <t>1714857</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>4.547,25</t>
+          <t>185,07</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -6074,7 +6074,7 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>R$ 4.547,25</t>
+          <t>R$ 185,07</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
@@ -6091,12 +6091,12 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>1715131</t>
+          <t>1714909</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>2.220,22</t>
+          <t>1.062,57</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -6106,7 +6106,7 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>R$ 2.220,22</t>
+          <t>R$ 1.062,57</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
@@ -6123,12 +6123,12 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>1715154</t>
+          <t>1715127</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>2.658,74</t>
+          <t>4.547,25</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -6138,7 +6138,7 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>R$ 2.658,74</t>
+          <t>R$ 4.547,25</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
@@ -6155,12 +6155,12 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>1715201</t>
+          <t>1715131</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>6.990,57</t>
+          <t>2.220,22</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -6170,7 +6170,7 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>R$ 6.990,57</t>
+          <t>R$ 2.220,22</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
@@ -6187,12 +6187,12 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>1715257I</t>
+          <t>1715154</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>6.765,65</t>
+          <t>2.658,74</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -6202,7 +6202,7 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>R$ 6.765,65</t>
+          <t>R$ 2.658,74</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
@@ -6219,12 +6219,12 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>1715278</t>
+          <t>1715201</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>2.961,13</t>
+          <t>6.990,57</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -6234,7 +6234,7 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>R$ 2.961,13</t>
+          <t>R$ 6.990,57</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
@@ -6251,12 +6251,12 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>1715327</t>
+          <t>1715257I</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>5.483,37</t>
+          <t>6.765,65</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -6266,7 +6266,7 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>R$ 5.483,37</t>
+          <t>R$ 6.765,65</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
@@ -6283,12 +6283,12 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>1715668</t>
+          <t>1715278</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>2.319,53</t>
+          <t>2.961,13</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -6298,7 +6298,7 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>R$ 2.319,53</t>
+          <t>R$ 2.961,13</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
@@ -6315,44 +6315,44 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>1715688</t>
+          <t>1715327</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>11.094,98</t>
+          <t>5.483,37</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>73.801,59</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>-R$ 62.706,61</t>
+          <t>R$ 5.483,37</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>-85.0%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>1715710</t>
+          <t>1715668</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>326,74</t>
+          <t>2.319,53</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -6362,7 +6362,7 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>R$ 326,74</t>
+          <t>R$ 2.319,53</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
@@ -6379,44 +6379,44 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>1715816C</t>
+          <t>1715688</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>30,22</t>
+          <t>11.094,98</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>73.801,59</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>R$ 30,22</t>
+          <t>-R$ 62.706,61</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-85.0%</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>1715816I</t>
+          <t>1715710</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>3.168,40</t>
+          <t>326,74</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -6426,7 +6426,7 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>R$ 3.168,40</t>
+          <t>R$ 326,74</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
@@ -6443,12 +6443,12 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>1715878</t>
+          <t>1715816C</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>1.786,71</t>
+          <t>30,22</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -6458,7 +6458,7 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>R$ 1.786,71</t>
+          <t>R$ 30,22</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
@@ -6475,44 +6475,44 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>1715899</t>
+          <t>1715816I</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>3.389,65</t>
+          <t>3.168,40</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>30.150,78</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>-R$ 26.761,13</t>
+          <t>R$ 3.168,40</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>-88.8%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>1715920</t>
+          <t>1715878</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>1.031,94</t>
+          <t>1.786,71</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -6522,7 +6522,7 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>R$ 1.031,94</t>
+          <t>R$ 1.786,71</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
@@ -6539,118 +6539,118 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>1715955I</t>
+          <t>1715899</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>4.431,48</t>
+          <t>3.389,65</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>30.150,78</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>R$ 4.431,48</t>
+          <t>-R$ 26.761,13</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-88.8%</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>1716557</t>
+          <t>1715920</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>81.673,94</t>
+          <t>1.031,94</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>219.995,37</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>-R$ 138.321,43</t>
+          <t>R$ 1.031,94</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>-62.9%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>1716612</t>
+          <t>1715955I</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>113.404,80</t>
+          <t>4.431,48</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>219.995,37</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>-R$ 106.590,57</t>
+          <t>R$ 4.431,48</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>-48.5%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>1717166</t>
+          <t>1716557</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>22.116,83</t>
+          <t>81.673,94</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>73.801,59</t>
+          <t>219.995,37</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>-R$ 51.684,76</t>
+          <t>-R$ 138.321,43</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
@@ -6660,29 +6660,29 @@
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>-70.0%</t>
+          <t>-62.9%</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>1717168</t>
+          <t>1716612</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>2.615,74</t>
+          <t>113.404,80</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>30.150,78</t>
+          <t>219.995,37</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>-R$ 27.535,04</t>
+          <t>-R$ 106.590,57</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
@@ -6692,29 +6692,29 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>-91.3%</t>
+          <t>-48.5%</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>1717315</t>
+          <t>1717166</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>13.183,29</t>
+          <t>22.116,83</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>13.214,86</t>
+          <t>73.801,59</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>-R$ 31,57</t>
+          <t>-R$ 51.684,76</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
@@ -6724,61 +6724,61 @@
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>-0.2%</t>
+          <t>-70.0%</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>1717332</t>
+          <t>1717168</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>2.496,51</t>
+          <t>2.615,74</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>30.150,78</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>R$ 2.496,51</t>
+          <t>-R$ 27.535,04</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-91.3%</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>1718019</t>
+          <t>1717315</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>4.408,31</t>
+          <t>13.183,29</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>28.774,45</t>
+          <t>13.214,86</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>-R$ 24.366,14</t>
+          <t>-R$ 31,57</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
@@ -6788,61 +6788,61 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>-84.7%</t>
+          <t>-0.2%</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>1718435</t>
+          <t>1717332</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>17.153,90</t>
+          <t>2.496,51</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>40.717,37</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>-R$ 23.563,47</t>
+          <t>R$ 2.496,51</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>-57.9%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>1718441</t>
+          <t>1718019</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>85.675,14</t>
+          <t>4.408,31</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>102.545,06</t>
+          <t>28.774,45</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>-R$ 16.869,92</t>
+          <t>-R$ 24.366,14</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
@@ -6852,83 +6852,83 @@
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>-16.5%</t>
+          <t>-84.7%</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>1718442</t>
+          <t>1718435</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>3.206,15</t>
+          <t>17.153,90</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>40.717,37</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>R$ 3.206,15</t>
+          <t>-R$ 23.563,47</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-57.9%</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>1718555</t>
+          <t>1718441</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>80,49</t>
+          <t>85.675,14</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>102.545,06</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>R$ 80,49</t>
+          <t>-R$ 16.869,92</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-16.5%</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>1718555I</t>
+          <t>1718442</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>2.781,60</t>
+          <t>3.206,15</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -6938,7 +6938,7 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>R$ 2.781,60</t>
+          <t>R$ 3.206,15</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
@@ -6955,12 +6955,12 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>1718561</t>
+          <t>1718555</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>15.227,27</t>
+          <t>80,49</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -6970,7 +6970,7 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>R$ 15.227,27</t>
+          <t>R$ 80,49</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
@@ -6987,12 +6987,12 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>1718783</t>
+          <t>1718555I</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>16.983,02</t>
+          <t>2.781,60</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -7002,7 +7002,7 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>R$ 16.983,02</t>
+          <t>R$ 2.781,60</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
@@ -7019,44 +7019,44 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>1718783C</t>
+          <t>1718561</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>7,32</t>
+          <t>15.227,27</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>40.717,37</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>-R$ 40.710,05</t>
+          <t>R$ 15.227,27</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>-100.0%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>1718803</t>
+          <t>1718783</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>3.825,18</t>
+          <t>16.983,02</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -7066,7 +7066,7 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>R$ 3.825,18</t>
+          <t>R$ 16.983,02</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
@@ -7083,22 +7083,22 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>1718950</t>
+          <t>1718783C</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>65.537,44</t>
+          <t>7,32</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>104.023,78</t>
+          <t>40.717,37</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>-R$ 38.486,34</t>
+          <t>-R$ 40.710,05</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
@@ -7108,61 +7108,61 @@
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>-37.0%</t>
+          <t>-100.0%</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>1718951</t>
+          <t>1718803</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>257,86</t>
+          <t>3.825,18</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>59.203,65</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>-R$ 58.945,79</t>
+          <t>R$ 3.825,18</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>-99.6%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>1718954</t>
+          <t>1718950</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>16.304,49</t>
+          <t>65.537,44</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>45.853,04</t>
+          <t>104.023,78</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>-R$ 29.548,55</t>
+          <t>-R$ 38.486,34</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
@@ -7172,29 +7172,29 @@
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>-64.4%</t>
+          <t>-37.0%</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>1718956</t>
+          <t>1718951</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>34.745,40</t>
+          <t>257,86</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>104.023,78</t>
+          <t>59.203,65</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>-R$ 69.278,38</t>
+          <t>-R$ 58.945,79</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
@@ -7204,19 +7204,19 @@
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>-66.6%</t>
+          <t>-99.6%</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>1718958</t>
+          <t>1718954</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>28.287,18</t>
+          <t>16.304,49</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -7226,7 +7226,7 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>-R$ 17.565,86</t>
+          <t>-R$ 29.548,55</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
@@ -7236,61 +7236,61 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>-38.3%</t>
+          <t>-64.4%</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>1719070</t>
+          <t>1718956</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>3.077,85</t>
+          <t>34.745,40</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>104.023,78</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>R$ 3.077,85</t>
+          <t>-R$ 69.278,38</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-66.6%</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>1719077</t>
+          <t>1718958</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>12.241,72</t>
+          <t>28.287,18</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>55.391,23</t>
+          <t>45.853,04</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>-R$ 43.149,51</t>
+          <t>-R$ 17.565,86</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
@@ -7300,93 +7300,93 @@
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>-77.9%</t>
+          <t>-38.3%</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>1719097</t>
+          <t>1719070</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>7.450,28</t>
+          <t>3.077,85</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>17.534,63</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>-R$ 10.084,35</t>
+          <t>R$ 3.077,85</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>-57.5%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>1719135</t>
+          <t>1719077</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>960,92</t>
+          <t>12.241,72</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>55.391,23</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>R$ 960,92</t>
+          <t>-R$ 43.149,51</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-77.9%</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>1719154</t>
+          <t>1719097</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>2.574,70</t>
+          <t>7.450,28</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>73.801,59</t>
+          <t>17.534,63</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>-R$ 71.226,89</t>
+          <t>-R$ 10.084,35</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
@@ -7396,61 +7396,61 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>-96.5%</t>
+          <t>-57.5%</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>1719155</t>
+          <t>1719135</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>2.368,97</t>
+          <t>960,92</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>30.150,78</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>-R$ 27.781,81</t>
+          <t>R$ 960,92</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>-92.1%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>1719159</t>
+          <t>1719154</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>2.240,81</t>
+          <t>2.574,70</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>22.187,97</t>
+          <t>73.801,59</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>-R$ 19.947,16</t>
+          <t>-R$ 71.226,89</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
@@ -7460,19 +7460,19 @@
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>-89.9%</t>
+          <t>-96.5%</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>1719213</t>
+          <t>1719155</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>7.323,19</t>
+          <t>2.368,97</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -7482,7 +7482,7 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>-R$ 22.827,59</t>
+          <t>-R$ 27.781,81</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
@@ -7492,29 +7492,29 @@
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>-75.7%</t>
+          <t>-92.1%</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>1719214</t>
+          <t>1719159</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>6.124,60</t>
+          <t>2.240,81</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>28.774,45</t>
+          <t>22.187,97</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>-R$ 22.649,85</t>
+          <t>-R$ 19.947,16</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
@@ -7524,29 +7524,29 @@
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>-78.7%</t>
+          <t>-89.9%</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>1719488</t>
+          <t>1719213</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>10.023,26</t>
+          <t>7.323,19</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>205.265,15</t>
+          <t>30.150,78</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>-R$ 195.241,89</t>
+          <t>-R$ 22.827,59</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
@@ -7556,29 +7556,29 @@
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>-95.1%</t>
+          <t>-75.7%</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>1719775</t>
+          <t>1719214</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>6.946,00</t>
+          <t>6.124,60</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>10.782,30</t>
+          <t>28.774,45</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>-R$ 3.836,30</t>
+          <t>-R$ 22.649,85</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
@@ -7588,157 +7588,157 @@
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>-35.6%</t>
+          <t>-78.7%</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>1719881</t>
+          <t>1719488</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>3.239,73</t>
+          <t>10.023,26</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>205.265,15</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>R$ 3.239,73</t>
+          <t>-R$ 195.241,89</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-95.1%</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>1719881H</t>
+          <t>1719775</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>38.258,42</t>
+          <t>6.946,00</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>10.782,30</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>R$ 38.258,42</t>
+          <t>-R$ 3.836,30</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-35.6%</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>1720116</t>
+          <t>1719881</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>1.844,52</t>
+          <t>3.239,73</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>28.774,45</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>-R$ 26.929,93</t>
+          <t>R$ 3.239,73</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>-93.6%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>1720721</t>
+          <t>1719881H</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>2.015,45</t>
+          <t>38.258,42</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>17.534,63</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>-R$ 15.519,18</t>
+          <t>R$ 38.258,42</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>-88.5%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>1720909</t>
+          <t>1720116</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>2.851,89</t>
+          <t>1.844,52</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>7.731,21</t>
+          <t>28.774,45</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>-R$ 4.879,32</t>
+          <t>-R$ 26.929,93</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
@@ -7748,29 +7748,29 @@
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>-63.1%</t>
+          <t>-93.6%</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>1720914</t>
+          <t>1720721</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>16.536,50</t>
+          <t>2.015,45</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>55.022,87</t>
+          <t>17.534,63</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>-R$ 38.486,37</t>
+          <t>-R$ 15.519,18</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
@@ -7780,61 +7780,61 @@
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>-69.9%</t>
+          <t>-88.5%</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>1720920</t>
+          <t>1720909</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>644,89</t>
+          <t>2.851,89</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>7.731,21</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>R$ 644,89</t>
+          <t>-R$ 4.879,32</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-63.1%</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>1721175</t>
+          <t>1720914</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>1.191,73</t>
+          <t>16.536,50</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>22.187,97</t>
+          <t>55.022,87</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>-R$ 20.996,24</t>
+          <t>-R$ 38.486,37</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
@@ -7844,61 +7844,61 @@
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>-94.6%</t>
+          <t>-69.9%</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>1721180</t>
+          <t>1720920</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>7.835,70</t>
+          <t>644,89</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>13.305,24</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>-R$ 5.469,54</t>
+          <t>R$ 644,89</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>-41.1%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>1721595</t>
+          <t>1721175</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>2.704,41</t>
+          <t>1.191,73</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>16.337,54</t>
+          <t>22.187,97</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>-R$ 13.633,13</t>
+          <t>-R$ 20.996,24</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
@@ -7908,61 +7908,61 @@
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>-83.4%</t>
+          <t>-94.6%</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>1721631</t>
+          <t>1721180</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>12.649,43</t>
+          <t>7.835,70</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>13.305,24</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>R$ 12.649,43</t>
+          <t>-R$ 5.469,54</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-41.1%</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>1721631C</t>
+          <t>1721595</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>100,65</t>
+          <t>2.704,41</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>17.534,63</t>
+          <t>16.337,54</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>-R$ 17.433,98</t>
+          <t>-R$ 13.633,13</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
@@ -7972,61 +7972,61 @@
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>-99.4%</t>
+          <t>-83.4%</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>1721869</t>
+          <t>1721631</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>940,27</t>
+          <t>12.649,43</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>25.002,10</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>-R$ 24.061,83</t>
+          <t>R$ 12.649,43</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>-96.2%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>1721884</t>
+          <t>1721631C</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>41.481,66</t>
+          <t>100,65</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>205.265,15</t>
+          <t>17.534,63</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>-R$ 163.783,49</t>
+          <t>-R$ 17.433,98</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
@@ -8036,29 +8036,29 @@
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>-79.8%</t>
+          <t>-99.4%</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>1721886</t>
+          <t>1721869</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>15.863,55</t>
+          <t>940,27</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>55.022,87</t>
+          <t>25.002,10</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>-R$ 39.159,32</t>
+          <t>-R$ 24.061,83</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
@@ -8068,29 +8068,29 @@
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>-71.2%</t>
+          <t>-96.2%</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>1721887</t>
+          <t>1721884</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>15.229,27</t>
+          <t>41.481,66</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>60.918,10</t>
+          <t>205.265,15</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>-R$ 45.688,83</t>
+          <t>-R$ 163.783,49</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
@@ -8100,29 +8100,29 @@
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>-75.0%</t>
+          <t>-79.8%</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>1722165</t>
+          <t>1721886</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>23.880,34</t>
+          <t>15.863,55</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>294.803,26</t>
+          <t>55.022,87</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>-R$ 270.922,92</t>
+          <t>-R$ 39.159,32</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
@@ -8132,61 +8132,61 @@
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>-91.9%</t>
+          <t>-71.2%</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>1722169</t>
+          <t>1721887</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>39.464,29</t>
+          <t>15.229,27</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>60.918,10</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>R$ 39.464,29</t>
+          <t>-R$ 45.688,83</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-75.0%</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>1722320</t>
+          <t>1722165</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>12.790,83</t>
+          <t>23.880,34</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>30.150,78</t>
+          <t>294.803,26</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>-R$ 17.359,95</t>
+          <t>-R$ 270.922,92</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
@@ -8196,61 +8196,61 @@
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>-57.6%</t>
+          <t>-91.9%</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>1722321</t>
+          <t>1722169</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>8.119,58</t>
+          <t>39.464,29</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>60.918,10</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>-R$ 52.798,52</t>
+          <t>R$ 39.464,29</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>-86.7%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>1722779</t>
+          <t>1722320</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>15.490,41</t>
+          <t>12.790,83</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>205.265,15</t>
+          <t>30.150,78</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>-R$ 189.774,74</t>
+          <t>-R$ 17.359,95</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
@@ -8260,29 +8260,29 @@
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>-92.5%</t>
+          <t>-57.6%</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>1722803</t>
+          <t>1722321</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>1.585,72</t>
+          <t>8.119,58</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>52.950,36</t>
+          <t>60.918,10</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>-R$ 51.364,64</t>
+          <t>-R$ 52.798,52</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
@@ -8292,29 +8292,29 @@
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>-97.0%</t>
+          <t>-86.7%</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>1722904</t>
+          <t>1722779</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>2.417,20</t>
+          <t>15.490,41</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>25.002,10</t>
+          <t>205.265,15</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>-R$ 22.584,90</t>
+          <t>-R$ 189.774,74</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
@@ -8324,29 +8324,29 @@
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>-90.3%</t>
+          <t>-92.5%</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>1722905</t>
+          <t>1722803</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>2.816,32</t>
+          <t>1.585,72</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>46.847,53</t>
+          <t>52.950,36</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>-R$ 44.031,21</t>
+          <t>-R$ 51.364,64</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
@@ -8356,61 +8356,61 @@
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>-94.0%</t>
+          <t>-97.0%</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>1722924</t>
+          <t>1722904</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>19.829,31</t>
+          <t>2.417,20</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>19.642,99</t>
+          <t>25.002,10</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>R$ 186,32</t>
+          <t>-R$ 22.584,90</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>+0.9%</t>
+          <t>-90.3%</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>1723691</t>
+          <t>1722905</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>19.599,32</t>
+          <t>2.816,32</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>151.495,34</t>
+          <t>46.847,53</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>-R$ 131.896,02</t>
+          <t>-R$ 44.031,21</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
@@ -8420,61 +8420,61 @@
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>-87.1%</t>
+          <t>-94.0%</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>1723694</t>
+          <t>1722924</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>3.867,23</t>
+          <t>19.829,31</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>7.731,21</t>
+          <t>19.642,99</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>-R$ 3.863,98</t>
+          <t>R$ 186,32</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>-50.0%</t>
+          <t>+0.9%</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>1723722</t>
+          <t>1723691</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>3.175,84</t>
+          <t>19.599,32</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>10.782,30</t>
+          <t>151.495,34</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>-R$ 7.606,46</t>
+          <t>-R$ 131.896,02</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
@@ -8484,29 +8484,29 @@
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>-70.5%</t>
+          <t>-87.1%</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>1723724</t>
+          <t>1723694</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>3.376,37</t>
+          <t>3.867,23</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>104.023,78</t>
+          <t>7.731,21</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>-R$ 100.647,41</t>
+          <t>-R$ 3.863,98</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
@@ -8516,29 +8516,29 @@
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>-96.8%</t>
+          <t>-50.0%</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>1723726</t>
+          <t>1723722</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>7.911,81</t>
+          <t>3.175,84</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>46.847,53</t>
+          <t>10.782,30</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>-R$ 38.935,72</t>
+          <t>-R$ 7.606,46</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
@@ -8548,29 +8548,29 @@
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>-83.1%</t>
+          <t>-70.5%</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>1723727</t>
+          <t>1723724</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>2.821,44</t>
+          <t>3.376,37</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>45.853,04</t>
+          <t>104.023,78</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>-R$ 43.031,60</t>
+          <t>-R$ 100.647,41</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
@@ -8580,29 +8580,29 @@
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>-93.8%</t>
+          <t>-96.8%</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>1724051I</t>
+          <t>1723726</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>2.432,48</t>
+          <t>9.630,09</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>151.495,34</t>
+          <t>46.847,53</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>-R$ 149.062,86</t>
+          <t>-R$ 37.217,44</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
@@ -8612,29 +8612,29 @@
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>-98.4%</t>
+          <t>-79.4%</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>1724053</t>
+          <t>1723727</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>3.088,86</t>
+          <t>2.821,44</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>151.495,34</t>
+          <t>45.853,04</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>-R$ 148.406,48</t>
+          <t>-R$ 43.031,60</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
@@ -8644,29 +8644,29 @@
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>-98.0%</t>
+          <t>-93.8%</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>1724172</t>
+          <t>1724051I</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>23.068,97</t>
+          <t>2.432,48</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>60.918,10</t>
+          <t>151.495,34</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>-R$ 37.849,13</t>
+          <t>-R$ 149.062,86</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
@@ -8676,51 +8676,51 @@
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>-62.1%</t>
+          <t>-98.4%</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>1724341</t>
+          <t>1724053</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>40.758,00</t>
+          <t>3.088,86</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>151.495,34</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>R$ 40.758,00</t>
+          <t>-R$ 148.406,48</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-98.0%</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>1724356</t>
+          <t>1724172</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>7.614,80</t>
+          <t>23.068,97</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
@@ -8730,7 +8730,7 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>-R$ 53.303,30</t>
+          <t>-R$ 37.849,13</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
@@ -8740,61 +8740,61 @@
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>-87.5%</t>
+          <t>-62.1%</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>1724491</t>
+          <t>1724341</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>14.410,93</t>
+          <t>40.758,00</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>24.535,37</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>-R$ 10.124,44</t>
+          <t>R$ 40.758,00</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>-41.3%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>1724537</t>
+          <t>1724356</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>8.464,00</t>
+          <t>7.614,80</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>19.215,26</t>
+          <t>60.918,10</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>-R$ 10.751,26</t>
+          <t>-R$ 53.303,30</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
@@ -8804,29 +8804,29 @@
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>-56.0%</t>
+          <t>-87.5%</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>1724550</t>
+          <t>1724491</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>17.067,84</t>
+          <t>14.410,93</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>55.391,23</t>
+          <t>24.535,37</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>-R$ 38.323,39</t>
+          <t>-R$ 10.124,44</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
@@ -8836,29 +8836,29 @@
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>-69.2%</t>
+          <t>-41.3%</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>1724551</t>
+          <t>1724537</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>8.569,24</t>
+          <t>8.464,00</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>59.203,65</t>
+          <t>19.215,26</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>-R$ 50.634,41</t>
+          <t>-R$ 10.751,26</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
@@ -8868,29 +8868,29 @@
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>-85.5%</t>
+          <t>-56.0%</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>1724558</t>
+          <t>1724550</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>10.501,47</t>
+          <t>17.067,84</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>151.495,34</t>
+          <t>55.391,23</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>-R$ 140.993,87</t>
+          <t>-R$ 38.323,39</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
@@ -8900,29 +8900,29 @@
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>-93.1%</t>
+          <t>-69.2%</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>1724663</t>
+          <t>1724551</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>3.091,28</t>
+          <t>8.569,24</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>22.187,97</t>
+          <t>59.203,65</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>-R$ 19.096,69</t>
+          <t>-R$ 50.634,41</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
@@ -8932,29 +8932,29 @@
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>-86.1%</t>
+          <t>-85.5%</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>1724680</t>
+          <t>1724558</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>7.968,73</t>
+          <t>10.501,47</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>60.918,10</t>
+          <t>151.495,34</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>-R$ 52.949,37</t>
+          <t>-R$ 140.993,87</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
@@ -8964,29 +8964,29 @@
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>-86.9%</t>
+          <t>-93.1%</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>1725260</t>
+          <t>1724663</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>4.726,63</t>
+          <t>3.091,28</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>30.884,03</t>
+          <t>22.187,97</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>-R$ 26.157,40</t>
+          <t>-R$ 19.096,69</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
@@ -8996,29 +8996,29 @@
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>-84.7%</t>
+          <t>-86.1%</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>1725686</t>
+          <t>1724680</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>11.173,06</t>
+          <t>7.968,73</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>24.535,37</t>
+          <t>60.918,10</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>-R$ 13.362,31</t>
+          <t>-R$ 52.949,37</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
@@ -9028,29 +9028,29 @@
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>-54.5%</t>
+          <t>-86.9%</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>1725738C</t>
+          <t>1725260</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>146,69</t>
+          <t>4.726,63</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>25.002,10</t>
+          <t>30.884,03</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>-R$ 24.855,41</t>
+          <t>-R$ 26.157,40</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
@@ -9060,29 +9060,29 @@
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>-99.4%</t>
+          <t>-84.7%</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>1725738I</t>
+          <t>1725686</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>16.959,62</t>
+          <t>11.173,06</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>25.002,10</t>
+          <t>24.535,37</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>-R$ 8.042,48</t>
+          <t>-R$ 13.362,31</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
@@ -9092,61 +9092,61 @@
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>-32.2%</t>
+          <t>-54.5%</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>1725869</t>
+          <t>1725738C</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>2.488,83</t>
+          <t>146,69</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>25.002,10</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>R$ 2.488,83</t>
+          <t>-R$ 24.855,41</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-99.4%</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>1726007</t>
+          <t>1725738I</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>92.044,51</t>
+          <t>16.959,62</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>140.684,13</t>
+          <t>25.002,10</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>-R$ 48.639,62</t>
+          <t>-R$ 8.042,48</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
@@ -9156,61 +9156,61 @@
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>-34.6%</t>
+          <t>-32.2%</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>1726008</t>
+          <t>1725869</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>168.057,63</t>
+          <t>2.488,83</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>203.193,73</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>-R$ 35.136,10</t>
+          <t>R$ 2.488,83</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>-17.3%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>1726018</t>
+          <t>1726007</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>117.487,61</t>
+          <t>92.044,51</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>189.306,13</t>
+          <t>140.684,13</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>-R$ 71.818,52</t>
+          <t>-R$ 48.639,62</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
@@ -9220,29 +9220,29 @@
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>-37.9%</t>
+          <t>-34.6%</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>1726042</t>
+          <t>1726008</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>52.831,30</t>
+          <t>168.057,63</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>192.548,30</t>
+          <t>203.193,73</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>-R$ 139.717,00</t>
+          <t>-R$ 35.136,10</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
@@ -9252,29 +9252,29 @@
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>-72.6%</t>
+          <t>-17.3%</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>1726044</t>
+          <t>1726018</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>163.324,35</t>
+          <t>117.487,61</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>167.292,84</t>
+          <t>189.306,13</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>-R$ 3.968,49</t>
+          <t>-R$ 71.818,52</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
@@ -9284,29 +9284,29 @@
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>-2.4%</t>
+          <t>-37.9%</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>1726045</t>
+          <t>1726042</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>114.693,62</t>
+          <t>52.831,30</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>126.996,75</t>
+          <t>192.548,30</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>-R$ 12.303,13</t>
+          <t>-R$ 139.717,00</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
@@ -9316,29 +9316,29 @@
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>-9.7%</t>
+          <t>-72.6%</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>1726057</t>
+          <t>1726044</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>177.769,55</t>
+          <t>163.324,35</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>196.508,79</t>
+          <t>167.292,84</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>-R$ 18.739,24</t>
+          <t>-R$ 3.968,49</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
@@ -9348,29 +9348,29 @@
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>-9.5%</t>
+          <t>-2.4%</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>1726058</t>
+          <t>1726045</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>103.529,88</t>
+          <t>114.693,62</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>133.354,34</t>
+          <t>126.996,75</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>-R$ 29.824,46</t>
+          <t>-R$ 12.303,13</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
@@ -9380,29 +9380,29 @@
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>-22.4%</t>
+          <t>-9.7%</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>1726318</t>
+          <t>1726057</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>17.722,33</t>
+          <t>177.769,55</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>55.391,23</t>
+          <t>196.508,79</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>-R$ 37.668,90</t>
+          <t>-R$ 18.739,24</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
@@ -9412,29 +9412,29 @@
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>-68.0%</t>
+          <t>-9.5%</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>1726320</t>
+          <t>1726058</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>10.074,94</t>
+          <t>103.529,88</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>59.203,65</t>
+          <t>133.354,34</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>-R$ 49.128,71</t>
+          <t>-R$ 29.824,46</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
@@ -9444,29 +9444,29 @@
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>-83.0%</t>
+          <t>-22.4%</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>1726324</t>
+          <t>1726318</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>2.294,20</t>
+          <t>17.722,33</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>19.215,26</t>
+          <t>55.391,23</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>-R$ 16.921,06</t>
+          <t>-R$ 37.668,90</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
@@ -9476,29 +9476,29 @@
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>-88.1%</t>
+          <t>-68.0%</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>1726332</t>
+          <t>1726320</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>5.722,23</t>
+          <t>10.074,94</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>28.896,74</t>
+          <t>59.203,65</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>-R$ 23.174,51</t>
+          <t>-R$ 49.128,71</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
@@ -9508,29 +9508,29 @@
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>-80.2%</t>
+          <t>-83.0%</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>1726388</t>
+          <t>1726324</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>18.635,34</t>
+          <t>2.294,20</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>41.833,50</t>
+          <t>19.215,26</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>-R$ 23.198,16</t>
+          <t>-R$ 16.921,06</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
@@ -9540,29 +9540,29 @@
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>-55.5%</t>
+          <t>-88.1%</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>1726496</t>
+          <t>1726332</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>24.645,05</t>
+          <t>5.722,23</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>42.100,83</t>
+          <t>28.896,74</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>-R$ 17.455,78</t>
+          <t>-R$ 23.174,51</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
@@ -9572,61 +9572,61 @@
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>-41.5%</t>
+          <t>-80.2%</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>1726541</t>
+          <t>1726388</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>17.173,17</t>
+          <t>18.635,34</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>42,95</t>
+          <t>41.833,50</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>R$ 17.130,22</t>
+          <t>-R$ 23.198,16</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>+39884.1%</t>
+          <t>-55.5%</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>1726737</t>
+          <t>1726496</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>4.070,08</t>
+          <t>24.645,05</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>18.172,61</t>
+          <t>42.100,83</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>-R$ 14.102,53</t>
+          <t>-R$ 17.455,78</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
@@ -9636,179 +9636,179 @@
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>-77.6%</t>
+          <t>-41.5%</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>1726890</t>
+          <t>1726541</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>3.252,02</t>
+          <t>22.145,50</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>11.143,51</t>
+          <t>42,95</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>-R$ 7.891,49</t>
+          <t>R$ 22.102,55</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>-70.8%</t>
+          <t>+51461.1%</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>1727187</t>
+          <t>1726737</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>4.280,60</t>
+          <t>4.070,08</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>18.172,61</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>R$ 4.280,60</t>
+          <t>-R$ 14.102,53</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-77.6%</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>1727287</t>
+          <t>1726890</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>489,21</t>
+          <t>3.252,02</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>11.143,51</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>R$ 489,21</t>
+          <t>-R$ 7.891,49</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-70.8%</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>1727322</t>
+          <t>1727187</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>3.146,66</t>
+          <t>4.280,60</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>11.250,94</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>-R$ 8.104,28</t>
+          <t>R$ 4.280,60</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>-72.0%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>1727335</t>
+          <t>1727287</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>5.053,73</t>
+          <t>489,21</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>8.079,08</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>-R$ 3.025,35</t>
+          <t>R$ 489,21</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>-37.4%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>1727529</t>
+          <t>1727322</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>4.366,81</t>
+          <t>3.146,66</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
@@ -9818,7 +9818,7 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>-R$ 6.884,13</t>
+          <t>-R$ 8.104,28</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
@@ -9828,157 +9828,157 @@
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>-61.2%</t>
+          <t>-72.0%</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>1727778</t>
+          <t>1727335</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>3.846,49</t>
+          <t>5.053,73</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>8.079,08</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>R$ 3.846,49</t>
+          <t>-R$ 3.025,35</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-37.4%</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>1727808</t>
+          <t>1727529</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>4.366,81</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>11.250,94</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-R$ 6.884,13</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-61.2%</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>1727808I</t>
+          <t>1727778</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>2.562,33</t>
+          <t>3.846,49</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>8.676,98</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>-R$ 6.114,65</t>
+          <t>R$ 3.846,49</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>-70.5%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>1727881</t>
+          <t>1727808</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>2.707,35</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>2.757,73</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>-R$ 50,38</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>-1.8%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>1727882</t>
+          <t>1727808I</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>7.415,36</t>
+          <t>2.562,33</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>46.847,53</t>
+          <t>8.676,98</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>-R$ 39.432,17</t>
+          <t>-R$ 6.114,65</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
@@ -9988,29 +9988,29 @@
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>-84.2%</t>
+          <t>-70.5%</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>1728055</t>
+          <t>1727881</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>12.947,91</t>
+          <t>2.707,35</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>42.100,83</t>
+          <t>2.757,73</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>-R$ 29.152,92</t>
+          <t>-R$ 50,38</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
@@ -10020,61 +10020,61 @@
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>-69.2%</t>
+          <t>-1.8%</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>1728163</t>
+          <t>1727882</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>7.914,69</t>
+          <t>7.415,36</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>46.847,53</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>R$ 7.914,69</t>
+          <t>-R$ 39.432,17</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-84.2%</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>1728328</t>
+          <t>1728055</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>3.343,59</t>
+          <t>12.947,91</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>3.565,51</t>
+          <t>42.100,83</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>-R$ 221,92</t>
+          <t>-R$ 29.152,92</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
@@ -10084,61 +10084,61 @@
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>-6.2%</t>
+          <t>-69.2%</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>1728642</t>
+          <t>1728163</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>7.237,16</t>
+          <t>7.914,69</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>19.215,26</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>-R$ 11.978,10</t>
+          <t>R$ 7.914,69</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>-62.3%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>1729300</t>
+          <t>1728328</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>9.521,56</t>
+          <t>3.343,59</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>59.203,65</t>
+          <t>3.565,51</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>-R$ 49.682,09</t>
+          <t>-R$ 221,92</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
@@ -10148,29 +10148,29 @@
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>-83.9%</t>
+          <t>-6.2%</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>1729668</t>
+          <t>1728642</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>1.201,81</t>
+          <t>7.237,16</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>13.305,24</t>
+          <t>19.215,26</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>-R$ 12.103,43</t>
+          <t>-R$ 11.978,10</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
@@ -10180,93 +10180,93 @@
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>-91.0%</t>
+          <t>-62.3%</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>1729786</t>
+          <t>1729300</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>45.387,32</t>
+          <t>9.521,56</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>44.264,28</t>
+          <t>59.203,65</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>R$ 1.123,04</t>
+          <t>-R$ 49.682,09</t>
         </is>
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>+2.5%</t>
+          <t>-83.9%</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>1729828</t>
+          <t>1729553</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>914,81</t>
+          <t>11.151,84</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>11.250,94</t>
+          <t>10.490,41</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>-R$ 10.336,13</t>
+          <t>R$ 661,43</t>
         </is>
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>-91.9%</t>
+          <t>+6.3%</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>1730222</t>
+          <t>1729668</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>21.764,18</t>
+          <t>1.201,81</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>28.896,74</t>
+          <t>13.305,24</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>-R$ 7.132,56</t>
+          <t>-R$ 12.103,43</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">
@@ -10276,61 +10276,61 @@
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>-24.7%</t>
+          <t>-91.0%</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>1730270</t>
+          <t>1729786</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>10.340,91</t>
+          <t>45.387,32</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>42.100,83</t>
+          <t>44.264,28</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>-R$ 31.759,92</t>
+          <t>R$ 1.123,04</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>-75.4%</t>
+          <t>+2.5%</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>1730313</t>
+          <t>1729828</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>2.885,97</t>
+          <t>914,81</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>113.288,94</t>
+          <t>11.250,94</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>-R$ 110.402,97</t>
+          <t>-R$ 10.336,13</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">
@@ -10340,29 +10340,29 @@
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>-97.5%</t>
+          <t>-91.9%</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>1730642I</t>
+          <t>1730222</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>15.899,82</t>
+          <t>21.764,18</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>20.657,21</t>
+          <t>28.896,74</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>-R$ 4.757,39</t>
+          <t>-R$ 7.132,56</t>
         </is>
       </c>
       <c r="E311" t="inlineStr">
@@ -10372,29 +10372,29 @@
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>-23.0%</t>
+          <t>-24.7%</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>1730707</t>
+          <t>1730270</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>7.655,46</t>
+          <t>10.340,91</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>46.847,53</t>
+          <t>42.100,83</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>-R$ 39.192,07</t>
+          <t>-R$ 31.759,92</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
@@ -10404,29 +10404,29 @@
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>-83.7%</t>
+          <t>-75.4%</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>1730763</t>
+          <t>1730313</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>4.973,33</t>
+          <t>2.885,97</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>59.203,65</t>
+          <t>113.288,94</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>-R$ 54.230,32</t>
+          <t>-R$ 110.402,97</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
@@ -10436,29 +10436,29 @@
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>-91.6%</t>
+          <t>-97.5%</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>1730822</t>
+          <t>1730642I</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>31.373,82</t>
+          <t>15.899,82</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>68.930,71</t>
+          <t>20.657,21</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>-R$ 37.556,89</t>
+          <t>-R$ 4.757,39</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
@@ -10468,29 +10468,29 @@
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>-54.5%</t>
+          <t>-23.0%</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>1730908</t>
+          <t>1730707</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>4.386,39</t>
+          <t>7.655,46</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>17.270,31</t>
+          <t>46.847,53</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>-R$ 12.883,92</t>
+          <t>-R$ 39.192,07</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
@@ -10500,125 +10500,125 @@
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>-74.6%</t>
+          <t>-83.7%</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>1731653</t>
+          <t>1730763</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>5.940,43</t>
+          <t>4.973,33</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>59.203,65</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>R$ 5.940,43</t>
+          <t>-R$ 54.230,32</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-91.6%</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>1731746</t>
+          <t>1730822</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>1.571,63</t>
+          <t>31.373,82</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>1.571,60</t>
+          <t>68.930,71</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>R$ 0,03</t>
+          <t>-R$ 37.556,89</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>+0.0%</t>
+          <t>-54.5%</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>1732157</t>
+          <t>1730908</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>3.748,66</t>
+          <t>4.386,39</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>3.356,46</t>
+          <t>17.270,31</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>R$ 392,20</t>
+          <t>-R$ 12.883,92</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>+11.7%</t>
+          <t>-74.6%</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>1733419I</t>
+          <t>1731653</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>1.171,48</t>
+          <t>5.940,43</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>1.085,22</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>R$ 86,26</t>
+          <t>R$ 5.940,43</t>
         </is>
       </c>
       <c r="E319" t="inlineStr">
@@ -10628,125 +10628,125 @@
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>+7.9%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>1734449</t>
+          <t>1731746</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>10.662,83</t>
+          <t>1.571,63</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>46.847,53</t>
+          <t>1.571,60</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>-R$ 36.184,70</t>
+          <t>R$ 0,03</t>
         </is>
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>-77.2%</t>
+          <t>+0.0%</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>1734835I</t>
+          <t>1732157</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>16.200,62</t>
+          <t>3.748,66</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>17.293,31</t>
+          <t>3.356,46</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>-R$ 1.092,69</t>
+          <t>R$ 392,20</t>
         </is>
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>-6.3%</t>
+          <t>+11.7%</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>1737272</t>
+          <t>1733419I</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>4.617,63</t>
+          <t>1.171,48</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>11.970,80</t>
+          <t>1.085,22</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>-R$ 7.353,17</t>
+          <t>R$ 86,26</t>
         </is>
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>-61.4%</t>
+          <t>+7.9%</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>1737274</t>
+          <t>1734449</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>4.617,63</t>
+          <t>10.662,83</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>11.167,26</t>
+          <t>46.847,53</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>-R$ 6.549,63</t>
+          <t>-R$ 36.184,70</t>
         </is>
       </c>
       <c r="E323" t="inlineStr">
@@ -10756,29 +10756,29 @@
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>-58.7%</t>
+          <t>-77.2%</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>1737280</t>
+          <t>1734835I</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>2.886,03</t>
+          <t>16.200,62</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>45.915,63</t>
+          <t>17.293,31</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>-R$ 43.029,60</t>
+          <t>-R$ 1.092,69</t>
         </is>
       </c>
       <c r="E324" t="inlineStr">
@@ -10788,29 +10788,29 @@
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>-93.7%</t>
+          <t>-6.3%</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>1737483</t>
+          <t>1737272</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>5.194,82</t>
+          <t>4.617,63</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>25.279,27</t>
+          <t>11.970,80</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>-R$ 20.084,45</t>
+          <t>-R$ 7.353,17</t>
         </is>
       </c>
       <c r="E325" t="inlineStr">
@@ -10820,29 +10820,29 @@
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>-79.5%</t>
+          <t>-61.4%</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>1737484</t>
+          <t>1737274</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>5.194,82</t>
+          <t>4.617,63</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>25.279,27</t>
+          <t>11.167,26</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>-R$ 20.084,45</t>
+          <t>-R$ 6.549,63</t>
         </is>
       </c>
       <c r="E326" t="inlineStr">
@@ -10852,29 +10852,29 @@
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>-79.5%</t>
+          <t>-58.7%</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>1740643</t>
+          <t>1737280</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>4.617,63</t>
+          <t>2.886,03</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>113.288,94</t>
+          <t>45.915,63</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>-R$ 108.671,31</t>
+          <t>-R$ 43.029,60</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
@@ -10884,29 +10884,29 @@
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>-95.9%</t>
+          <t>-93.7%</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>1741124</t>
+          <t>1737483</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>2.885,97</t>
+          <t>5.194,82</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>113.288,94</t>
+          <t>25.279,27</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>-R$ 110.402,97</t>
+          <t>-R$ 20.084,45</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
@@ -10916,37 +10916,133 @@
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>-97.5%</t>
+          <t>-79.5%</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
+          <t>1737484</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>5.194,82</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>25.279,27</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>-R$ 20.084,45</t>
+        </is>
+      </c>
+      <c r="E329" t="inlineStr">
+        <is>
+          <t>❌ PREJUÍZO</t>
+        </is>
+      </c>
+      <c r="F329" t="inlineStr">
+        <is>
+          <t>-79.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>1740643</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>4.617,63</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>113.288,94</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>-R$ 108.671,31</t>
+        </is>
+      </c>
+      <c r="E330" t="inlineStr">
+        <is>
+          <t>❌ PREJUÍZO</t>
+        </is>
+      </c>
+      <c r="F330" t="inlineStr">
+        <is>
+          <t>-95.9%</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>1741124</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>2.885,97</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>113.288,94</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>-R$ 110.402,97</t>
+        </is>
+      </c>
+      <c r="E331" t="inlineStr">
+        <is>
+          <t>❌ PREJUÍZO</t>
+        </is>
+      </c>
+      <c r="F331" t="inlineStr">
+        <is>
+          <t>-97.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
           <t>1741248</t>
         </is>
       </c>
-      <c r="B329" t="inlineStr">
+      <c r="B332" t="inlineStr">
         <is>
           <t>4.617,63</t>
         </is>
       </c>
-      <c r="C329" t="inlineStr">
+      <c r="C332" t="inlineStr">
         <is>
           <t>113.288,94</t>
         </is>
       </c>
-      <c r="D329" t="inlineStr">
+      <c r="D332" t="inlineStr">
         <is>
           <t>-R$ 108.671,31</t>
         </is>
       </c>
-      <c r="E329" t="inlineStr">
-        <is>
-          <t>❌ PREJUÍZO</t>
-        </is>
-      </c>
-      <c r="F329" t="inlineStr">
+      <c r="E332" t="inlineStr">
+        <is>
+          <t>❌ PREJUÍZO</t>
+        </is>
+      </c>
+      <c r="F332" t="inlineStr">
         <is>
           <t>-95.9%</t>
         </is>
